--- a/data/CG-cttos.xlsx
+++ b/data/CG-cttos.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="275">
+  <fonts count="277">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -35,6 +35,14 @@
       <name val="Calibri"/>
       <sz val="12.5"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -1257,7 +1265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -2102,6 +2110,12 @@
     <xf numFmtId="0" fontId="274" fillId="5" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment horizontal="left" wrapText="true" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="275" fillId="5" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="left" wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="5" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="left" wrapText="true" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -35550,7 +35564,7 @@
         <v>1.53200585E9</v>
       </c>
       <c r="AH130" s="7" t="n">
-        <v>1.53200585E9</v>
+        <v>0.0</v>
       </c>
       <c r="AI130" s="7" t="n">
         <v>0.0</v>
@@ -35596,7 +35610,7 @@
         <v>46194.0</v>
       </c>
       <c r="AT130" s="5" t="n">
-        <v>45650.0</v>
+        <v>45709.0</v>
       </c>
       <c r="AU130" s="5" t="n">
         <v>45589.0</v>
@@ -35808,7 +35822,7 @@
         <v>2.2509438604E10</v>
       </c>
       <c r="AH131" s="7" t="n">
-        <v>2.2509438604E10</v>
+        <v>0.0</v>
       </c>
       <c r="AI131" s="7" t="n">
         <v>0.0</v>
@@ -35854,7 +35868,7 @@
         <v>46194.0</v>
       </c>
       <c r="AT131" s="5" t="n">
-        <v>45649.0</v>
+        <v>45709.0</v>
       </c>
       <c r="AU131" s="5" t="n">
         <v>45628.0</v>
@@ -65344,55 +65358,57 @@
       </c>
       <c r="W244" s="11" t="inlineStr">
         <is>
-          <t>CPS-492-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X244" s="11" t="inlineStr">
         <is>
-          <t>CPS-492-2025</t>
-        </is>
-      </c>
-      <c r="Y244" s="5" t="n">
-        <v>45827.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="Y244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="Z244" s="11" t="inlineStr">
         <is>
-          <t>CO1.RECEIPT.28943175</t>
+          <t/>
         </is>
       </c>
       <c r="AA244" s="11" t="inlineStr">
         <is>
-          <t>Contratación directa</t>
+          <t/>
         </is>
       </c>
       <c r="AB244" s="11" t="inlineStr">
         <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+          <t/>
         </is>
       </c>
       <c r="AC244" s="11" t="inlineStr">
         <is>
-          <t>Prestación de Servicios</t>
+          <t>SPGR Por definir</t>
         </is>
       </c>
       <c r="AD244" s="11" t="inlineStr">
         <is>
-          <t>CPS-492-2025</t>
+          <t>LP-009-2025</t>
         </is>
       </c>
       <c r="AE244" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES COMO INGENIERO CIVIL PARA EL APOYO A LA SUPERVISION DESDE LA SECRETARIA DE INFRAESTRUCTURA EN EL MARCO DEL PROYECTO CONSTRUCCION DE LA CASA PARTICIPACION CIUDADANA EN EL MUNICIPIO DE SINCELEJO DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF244" s="7" t="n">
-        <v>3.888E7</v>
-      </c>
-      <c r="AG244" s="7" t="n">
-        <v>3.888E7</v>
-      </c>
-      <c r="AH244" s="7" t="n">
-        <v>3.888E7</v>
+          <t>CONSTRUCCION DE LA SEDE DE LA CASA DE PARTICIPACION CIUDADANA EN EL MUNICIPIO DE SINCELEJO.</t>
+        </is>
+      </c>
+      <c r="AF244" s="8" t="n">
+        <v>6.3746003962E8</v>
+      </c>
+      <c r="AG244" s="8" t="n">
+        <v>6.3746003962E8</v>
+      </c>
+      <c r="AH244" s="8" t="n">
+        <v>6.3746003962E8</v>
       </c>
       <c r="AI244" s="7" t="n">
         <v>0.0</v>
@@ -65410,35 +65426,41 @@
       </c>
       <c r="AM244" s="11" t="inlineStr">
         <is>
-          <t>1104873633</t>
+          <t>901548710</t>
         </is>
       </c>
       <c r="AN244" s="11" t="inlineStr">
         <is>
-          <t>SOTOMAYOR CUADRADO ADOLFO JOSE</t>
+          <t>MANA CONSTRUCCIONES S.A.S.</t>
         </is>
       </c>
       <c r="AO244" s="11" t="inlineStr">
         <is>
-          <t>SOTOMAYOR CUADRADO ADOLFO JOSE</t>
+          <t>María Julia Fayad Padilla</t>
         </is>
       </c>
       <c r="AP244" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
-        </is>
-      </c>
-      <c r="AQ244" s="5" t="n">
-        <v>45827.0</v>
-      </c>
-      <c r="AR244" s="5" t="n">
-        <v>46009.0</v>
-      </c>
-      <c r="AS244" s="5" t="n">
-        <v>46009.0</v>
+          <t xml:space="preserve">Sociedad Por Acciones Simplificadas                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="AQ244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AT244" s="5" t="n">
-        <v>45827.0</v>
+        <v>46161.0</v>
       </c>
       <c r="AU244" s="11" t="inlineStr">
         <is>
@@ -65450,20 +65472,24 @@
           <t/>
         </is>
       </c>
-      <c r="AW244" s="7" t="n">
-        <v>6.0</v>
+      <c r="AW244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AX244" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
-        </is>
-      </c>
-      <c r="AY244" s="7" t="n">
-        <v>4.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AY244" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AZ244" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t/>
         </is>
       </c>
       <c r="BA244" s="11" t="inlineStr">
@@ -65495,7 +65521,7 @@
       </c>
       <c r="BH244" s="11" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO ROMERO ROMERO</t>
+          <t/>
         </is>
       </c>
       <c r="BI244" s="11" t="inlineStr">
@@ -65505,7 +65531,7 @@
       </c>
       <c r="BJ244" s="11" t="inlineStr">
         <is>
-          <t>22/06/2025</t>
+          <t>23/05/2026</t>
         </is>
       </c>
     </row>
@@ -65573,17 +65599,17 @@
       </c>
       <c r="N245" s="11" t="inlineStr">
         <is>
-          <t>2024002700184</t>
+          <t>2024002700183</t>
         </is>
       </c>
       <c r="O245" s="11" t="inlineStr">
         <is>
-          <t>Fortalecimiento Productivo Piscícola para la  Recuperación de Especies Nativas y  la  Seguridad Alimentaria en Asociaciones de  Pescadores Artesanales  de la Ecorregión Mojana del Departamento de   Sucre</t>
+          <t>Construcción  de la casa de participación ciudadana en el municipio de Sincelejo departamento de  Sucre</t>
         </is>
       </c>
       <c r="P245" s="11" t="inlineStr">
         <is>
-          <t>AGRICULTURA Y DESARROLLO RURAL</t>
+          <t>GOBIERNO TERRITORIAL</t>
         </is>
       </c>
       <c r="Q245" s="11" t="inlineStr">
@@ -65592,73 +65618,71 @@
         </is>
       </c>
       <c r="R245" s="8" t="n">
-        <v>2.65369159731E9</v>
+        <v>2.43963756809E9</v>
       </c>
       <c r="S245" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="T245" s="7" t="n">
-        <v>9.29670814E8</v>
+        <v>0.0</v>
       </c>
       <c r="U245" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="V245" s="8" t="n">
-        <v>3.58336241131E9</v>
+        <v>2.43963756809E9</v>
       </c>
       <c r="W245" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CPS-492-2025</t>
         </is>
       </c>
       <c r="X245" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y245" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>CPS-492-2025</t>
+        </is>
+      </c>
+      <c r="Y245" s="5" t="n">
+        <v>45827.0</v>
       </c>
       <c r="Z245" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>CO1.RECEIPT.28943175</t>
         </is>
       </c>
       <c r="AA245" s="11" t="inlineStr">
         <is>
-          <t>Concurso de méritos</t>
+          <t>Contratación directa</t>
         </is>
       </c>
       <c r="AB245" s="11" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
         </is>
       </c>
       <c r="AC245" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interventoría                                                         </t>
+          <t>Prestación de Servicios</t>
         </is>
       </c>
       <c r="AD245" s="11" t="inlineStr">
         <is>
-          <t>CM-002-2025</t>
+          <t>CPS-492-2025</t>
         </is>
       </c>
       <c r="AE245" s="11" t="inlineStr">
         <is>
-          <t>INTERVENTORIA TECNICA, ADMINISTRATIVA Y FINANCIERA DEL PROYECTO DE FORTALECIMIENTO PRODUCTIVO PISCÍCOLA PARA LA RECUPERACIÓN DE ESPECIES NATIVAS Y LA SEGURIDAD ALIMENTARIA EN ASOCIACIONES DE PESCADORES ARTESANALES DE LA ECORREGIÓN MOJANA DEL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES COMO INGENIERO CIVIL PARA EL APOYO A LA SUPERVISION DESDE LA SECRETARIA DE INFRAESTRUCTURA EN EL MARCO DEL PROYECTO CONSTRUCCION DE LA CASA PARTICIPACION CIUDADANA EN EL MUNICIPIO DE SINCELEJO DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF245" s="7" t="n">
-        <v>1.63451022E8</v>
+        <v>3.888E7</v>
       </c>
       <c r="AG245" s="7" t="n">
-        <v>1.63451022E8</v>
+        <v>3.888E7</v>
       </c>
       <c r="AH245" s="7" t="n">
-        <v>1.63451022E8</v>
+        <v>3.888E7</v>
       </c>
       <c r="AI245" s="7" t="n">
         <v>0.0</v>
@@ -65676,42 +65700,44 @@
       </c>
       <c r="AM245" s="11" t="inlineStr">
         <is>
-          <t>823002290</t>
+          <t>1104873633</t>
         </is>
       </c>
       <c r="AN245" s="11" t="inlineStr">
         <is>
-          <t>FUNDACION AGROTEC</t>
+          <t>SOTOMAYOR CUADRADO ADOLFO JOSE</t>
         </is>
       </c>
       <c r="AO245" s="11" t="inlineStr">
         <is>
-          <t>ALVARO JOSE TRILLO GALVAN</t>
+          <t>SOTOMAYOR CUADRADO ADOLFO JOSE</t>
         </is>
       </c>
       <c r="AP245" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entidad sin ánimo de lucro                                                                                                                            </t>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
         </is>
       </c>
       <c r="AQ245" s="5" t="n">
-        <v>45835.0</v>
+        <v>45827.0</v>
       </c>
       <c r="AR245" s="5" t="n">
-        <v>46017.0</v>
+        <v>46009.0</v>
       </c>
       <c r="AS245" s="5" t="n">
-        <v>46017.0</v>
+        <v>46009.0</v>
       </c>
       <c r="AT245" s="5" t="n">
-        <v>45828.0</v>
-      </c>
-      <c r="AU245" s="5" t="n">
-        <v>45828.0</v>
+        <v>45827.0</v>
+      </c>
+      <c r="AU245" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AV245" s="11" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t/>
         </is>
       </c>
       <c r="AW245" s="7" t="n">
@@ -65723,7 +65749,7 @@
         </is>
       </c>
       <c r="AY245" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ245" s="11" t="inlineStr">
         <is>
@@ -65735,27 +65761,31 @@
           <t>N</t>
         </is>
       </c>
-      <c r="BB245" s="5" t="n">
-        <v>46086.0</v>
-      </c>
-      <c r="BC245" s="5" t="n">
-        <v>46086.0</v>
+      <c r="BB245" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC245" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="BD245" s="7" t="n">
-        <v>5.4483674E7</v>
+        <v>0.0</v>
       </c>
       <c r="BE245" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF245" s="7" t="n">
-        <v>9317170.0</v>
+        <v>0.0</v>
       </c>
       <c r="BG245" s="7" t="n">
-        <v>5.4483674E7</v>
+        <v>0.0</v>
       </c>
       <c r="BH245" s="11" t="inlineStr">
         <is>
-          <t>ALVARO EDUARDO LOPEZ HERRERA</t>
+          <t>JORGE ALBERTO ROMERO ROMERO</t>
         </is>
       </c>
       <c r="BI245" s="11" t="inlineStr">
@@ -65765,7 +65795,7 @@
       </c>
       <c r="BJ245" s="11" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>22/06/2025</t>
         </is>
       </c>
     </row>
@@ -66043,17 +66073,17 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>REGIONALES</t>
+          <t>DEPARTAMENTALES</t>
         </is>
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Región Caribe</t>
+          <t>DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="D247" s="11" t="inlineStr">
         <is>
-          <t>Región Caribe</t>
+          <t>SUCRE</t>
         </is>
       </c>
       <c r="E247" s="11" t="inlineStr">
@@ -66099,17 +66129,17 @@
       </c>
       <c r="N247" s="11" t="inlineStr">
         <is>
-          <t>2025000020019</t>
+          <t>2024002700184</t>
         </is>
       </c>
       <c r="O247" s="11" t="inlineStr">
         <is>
-          <t>Implementación del programa de alimentación escolar -PAE- para el segundo semestre del 2025 en el Departamento de   Sucre</t>
+          <t>Fortalecimiento Productivo Piscícola para la  Recuperación de Especies Nativas y  la  Seguridad Alimentaria en Asociaciones de  Pescadores Artesanales  de la Ecorregión Mojana del Departamento de   Sucre</t>
         </is>
       </c>
       <c r="P247" s="11" t="inlineStr">
         <is>
-          <t>EDUCACIÓN</t>
+          <t>AGRICULTURA Y DESARROLLO RURAL</t>
         </is>
       </c>
       <c r="Q247" s="11" t="inlineStr">
@@ -66117,20 +66147,20 @@
           <t/>
         </is>
       </c>
-      <c r="R247" s="7" t="n">
-        <v>1.5884181916E10</v>
+      <c r="R247" s="8" t="n">
+        <v>2.65369159731E9</v>
       </c>
       <c r="S247" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="T247" s="7" t="n">
-        <v>0.0</v>
+        <v>9.29670814E8</v>
       </c>
       <c r="U247" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="V247" s="7" t="n">
-        <v>1.5884181916E10</v>
+      <c r="V247" s="8" t="n">
+        <v>3.58336241131E9</v>
       </c>
       <c r="W247" s="11" t="inlineStr">
         <is>
@@ -66154,37 +66184,37 @@
       </c>
       <c r="AA247" s="11" t="inlineStr">
         <is>
-          <t>Contratación directa</t>
+          <t>Concurso de méritos</t>
         </is>
       </c>
       <c r="AB247" s="11" t="inlineStr">
         <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="AC247" s="11" t="inlineStr">
         <is>
-          <t>Prestación de Servicios</t>
+          <t xml:space="preserve">Interventoría                                                         </t>
         </is>
       </c>
       <c r="AD247" s="11" t="inlineStr">
         <is>
-          <t>CPS-1142-2025</t>
+          <t>CM-002-2025</t>
         </is>
       </c>
       <c r="AE247" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES  PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR DE LA SECRETARIA DE EDUCACION DEPARTAMENTAL DE SUCRE</t>
+          <t>INTERVENTORIA TECNICA, ADMINISTRATIVA Y FINANCIERA DEL PROYECTO DE FORTALECIMIENTO PRODUCTIVO PISCÍCOLA PARA LA RECUPERACIÓN DE ESPECIES NATIVAS Y LA SEGURIDAD ALIMENTARIA EN ASOCIACIONES DE PESCADORES ARTESANALES DE LA ECORREGIÓN MOJANA DEL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF247" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.63451022E8</v>
       </c>
       <c r="AG247" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.63451022E8</v>
       </c>
       <c r="AH247" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.63451022E8</v>
       </c>
       <c r="AI247" s="7" t="n">
         <v>0.0</v>
@@ -66197,53 +66227,51 @@
       </c>
       <c r="AL247" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">En ejecución                                                          </t>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
       <c r="AM247" s="11" t="inlineStr">
         <is>
-          <t>1102839122</t>
+          <t>823002290</t>
         </is>
       </c>
       <c r="AN247" s="11" t="inlineStr">
         <is>
-          <t>HERNANDEZ TUIRAN ANDRES ALBERTO</t>
+          <t>FUNDACION AGROTEC</t>
         </is>
       </c>
       <c r="AO247" s="11" t="inlineStr">
         <is>
-          <t>HERNANDEZ TUIRAN ANDRES ALBERTO</t>
+          <t>ALVARO JOSE TRILLO GALVAN</t>
         </is>
       </c>
       <c r="AP247" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Entidad sin ánimo de lucro                                                                                                                            </t>
         </is>
       </c>
       <c r="AQ247" s="5" t="n">
-        <v>45989.0</v>
+        <v>45835.0</v>
       </c>
       <c r="AR247" s="5" t="n">
-        <v>46018.0</v>
+        <v>46017.0</v>
       </c>
       <c r="AS247" s="5" t="n">
-        <v>46018.0</v>
+        <v>46017.0</v>
       </c>
       <c r="AT247" s="5" t="n">
-        <v>45989.0</v>
-      </c>
-      <c r="AU247" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>45828.0</v>
+      </c>
+      <c r="AU247" s="5" t="n">
+        <v>45828.0</v>
       </c>
       <c r="AV247" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="AW247" s="7" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="AX247" s="11" t="inlineStr">
         <is>
@@ -66251,7 +66279,7 @@
         </is>
       </c>
       <c r="AY247" s="7" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="AZ247" s="11" t="inlineStr">
         <is>
@@ -66264,26 +66292,26 @@
         </is>
       </c>
       <c r="BB247" s="5" t="n">
-        <v>46049.0</v>
+        <v>46086.0</v>
       </c>
       <c r="BC247" s="5" t="n">
-        <v>46049.0</v>
+        <v>46086.0</v>
       </c>
       <c r="BD247" s="7" t="n">
-        <v>5237264.0</v>
+        <v>5.4483674E7</v>
       </c>
       <c r="BE247" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF247" s="7" t="n">
-        <v>340161.0</v>
+        <v>9317170.0</v>
       </c>
       <c r="BG247" s="7" t="n">
-        <v>5237264.0</v>
+        <v>5.4483674E7</v>
       </c>
       <c r="BH247" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>ALVARO EDUARDO LOPEZ HERRERA</t>
         </is>
       </c>
       <c r="BI247" s="11" t="inlineStr">
@@ -66293,7 +66321,7 @@
       </c>
       <c r="BJ247" s="11" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
     </row>
@@ -66951,12 +66979,12 @@
       </c>
       <c r="AD250" s="11" t="inlineStr">
         <is>
-          <t>CPS-1183-2025</t>
+          <t>CPS-1142-2025</t>
         </is>
       </c>
       <c r="AE250" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES  PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR DE LA SECRETARIA DE EDUCACION DEPARTAMENTAL DE SUCRE</t>
         </is>
       </c>
       <c r="AF250" s="7" t="n">
@@ -66984,35 +67012,35 @@
       </c>
       <c r="AM250" s="11" t="inlineStr">
         <is>
-          <t>1102828243</t>
+          <t>1102839122</t>
         </is>
       </c>
       <c r="AN250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuranis Astrid Morón Fuentes </t>
+          <t>HERNANDEZ TUIRAN ANDRES ALBERTO</t>
         </is>
       </c>
       <c r="AO250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuranis Astrid Morón Fuentes </t>
+          <t>HERNANDEZ TUIRAN ANDRES ALBERTO</t>
         </is>
       </c>
       <c r="AP250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+          <t/>
         </is>
       </c>
       <c r="AQ250" s="5" t="n">
-        <v>45992.0</v>
+        <v>45989.0</v>
       </c>
       <c r="AR250" s="5" t="n">
-        <v>46022.0</v>
+        <v>46018.0</v>
       </c>
       <c r="AS250" s="5" t="n">
-        <v>46022.0</v>
+        <v>46018.0</v>
       </c>
       <c r="AT250" s="5" t="n">
-        <v>45992.0</v>
+        <v>45989.0</v>
       </c>
       <c r="AU250" s="11" t="inlineStr">
         <is>
@@ -67025,11 +67053,11 @@
         </is>
       </c>
       <c r="AW250" s="7" t="n">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="AX250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="AY250" s="7" t="n">
@@ -67037,7 +67065,7 @@
       </c>
       <c r="AZ250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="BA250" s="11" t="inlineStr">
@@ -67046,10 +67074,10 @@
         </is>
       </c>
       <c r="BB250" s="5" t="n">
-        <v>46045.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BC250" s="5" t="n">
-        <v>46045.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BD250" s="7" t="n">
         <v>5237264.0</v>
@@ -67440,22 +67468,20 @@
       </c>
       <c r="W252" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CPS-918-2025</t>
         </is>
       </c>
       <c r="X252" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y252" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="Y252" s="5" t="n">
+        <v>45925.0</v>
       </c>
       <c r="Z252" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>CO1.SLCNTR.15808066</t>
         </is>
       </c>
       <c r="AA252" s="11" t="inlineStr">
@@ -67475,22 +67501,22 @@
       </c>
       <c r="AD252" s="11" t="inlineStr">
         <is>
-          <t>CPS-1122-2025</t>
+          <t>CPS-918-2025</t>
         </is>
       </c>
       <c r="AE252" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR  EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF252" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AG252" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AH252" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AI252" s="7" t="n">
         <v>0.0</v>
@@ -67503,40 +67529,40 @@
       </c>
       <c r="AL252" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">En ejecución                                                          </t>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
       <c r="AM252" s="11" t="inlineStr">
         <is>
-          <t>64703642</t>
+          <t>1102844070</t>
         </is>
       </c>
       <c r="AN252" s="11" t="inlineStr">
         <is>
-          <t>ORTEGA CASTIBLANCO KELLY JOHANA</t>
+          <t>FERNANDEZ ACOSTA GABRIELA</t>
         </is>
       </c>
       <c r="AO252" s="11" t="inlineStr">
         <is>
-          <t>ORTEGA CASTIBLANCO KELLY JOHANA</t>
+          <t>FERNANDEZ ACOSTA GABRIELA</t>
         </is>
       </c>
       <c r="AP252" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
         </is>
       </c>
       <c r="AQ252" s="5" t="n">
-        <v>45989.0</v>
+        <v>45930.0</v>
       </c>
       <c r="AR252" s="5" t="n">
-        <v>46018.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AS252" s="5" t="n">
-        <v>46018.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AT252" s="5" t="n">
-        <v>45989.0</v>
+        <v>45925.0</v>
       </c>
       <c r="AU252" s="11" t="inlineStr">
         <is>
@@ -67545,23 +67571,23 @@
       </c>
       <c r="AV252" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t/>
         </is>
       </c>
       <c r="AW252" s="7" t="n">
-        <v>1.0</v>
+        <v>75.0</v>
       </c>
       <c r="AX252" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="AY252" s="7" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="AZ252" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="BA252" s="11" t="inlineStr">
@@ -67570,22 +67596,22 @@
         </is>
       </c>
       <c r="BB252" s="5" t="n">
-        <v>46049.0</v>
+        <v>46000.0</v>
       </c>
       <c r="BC252" s="5" t="n">
-        <v>46049.0</v>
+        <v>46017.0</v>
       </c>
       <c r="BD252" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BE252" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF252" s="7" t="n">
-        <v>340161.0</v>
+      <c r="BF252" s="8" t="n">
+        <v>850400.29</v>
       </c>
       <c r="BG252" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BH252" s="11" t="inlineStr">
         <is>
@@ -67599,7 +67625,7 @@
       </c>
       <c r="BJ252" s="11" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
     </row>
@@ -67962,126 +67988,128 @@
       </c>
       <c r="W254" s="11" t="inlineStr">
         <is>
-          <t>CPS-924-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X254" s="11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y254" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z254" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA254" s="11" t="inlineStr">
+        <is>
+          <t>Contratación directa</t>
+        </is>
+      </c>
+      <c r="AB254" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+        </is>
+      </c>
+      <c r="AC254" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios</t>
+        </is>
+      </c>
+      <c r="AD254" s="11" t="inlineStr">
+        <is>
+          <t>CPS-1143-2025</t>
+        </is>
+      </c>
+      <c r="AE254" s="11" t="inlineStr">
+        <is>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR  EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF254" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AG254" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AH254" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AI254" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ254" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK254" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL254" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En ejecución                                                          </t>
+        </is>
+      </c>
+      <c r="AM254" s="11" t="inlineStr">
+        <is>
+          <t>1005659848</t>
+        </is>
+      </c>
+      <c r="AN254" s="11" t="inlineStr">
+        <is>
+          <t>ORDOÑEZ VERGARA MAYLEN JOSE</t>
+        </is>
+      </c>
+      <c r="AO254" s="11" t="inlineStr">
+        <is>
+          <t>ORDOÑEZ VERGARA MAYLEN JOSE</t>
+        </is>
+      </c>
+      <c r="AP254" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ254" s="5" t="n">
+        <v>45989.0</v>
+      </c>
+      <c r="AR254" s="5" t="n">
+        <v>46018.0</v>
+      </c>
+      <c r="AS254" s="5" t="n">
+        <v>46018.0</v>
+      </c>
+      <c r="AT254" s="5" t="n">
+        <v>45989.0</v>
+      </c>
+      <c r="AU254" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV254" s="11" t="inlineStr">
+        <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="Y254" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="Z254" s="11" t="inlineStr">
-        <is>
-          <t>CO1.SLCNTR.15801022</t>
-        </is>
-      </c>
-      <c r="AA254" s="11" t="inlineStr">
-        <is>
-          <t>Contratación directa</t>
-        </is>
-      </c>
-      <c r="AB254" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
-        </is>
-      </c>
-      <c r="AC254" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de Servicios</t>
-        </is>
-      </c>
-      <c r="AD254" s="11" t="inlineStr">
-        <is>
-          <t>CPS-924-2025</t>
-        </is>
-      </c>
-      <c r="AE254" s="11" t="inlineStr">
-        <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF254" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AG254" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AH254" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AI254" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ254" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK254" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL254" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contratado sin ejecución                                              </t>
-        </is>
-      </c>
-      <c r="AM254" s="11" t="inlineStr">
-        <is>
-          <t>1102820744</t>
-        </is>
-      </c>
-      <c r="AN254" s="11" t="inlineStr">
-        <is>
-          <t>BENITEZ FRANCO FABIO ANDRES</t>
-        </is>
-      </c>
-      <c r="AO254" s="11" t="inlineStr">
-        <is>
-          <t>BENITEZ FRANCO FABIO ANDRES</t>
-        </is>
-      </c>
-      <c r="AP254" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ254" s="5" t="n">
-        <v>45930.0</v>
-      </c>
-      <c r="AR254" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AS254" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AT254" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="AU254" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV254" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AW254" s="7" t="n">
-        <v>75.0</v>
+        <v>1.0</v>
       </c>
       <c r="AX254" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="AY254" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ254" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="BA254" s="11" t="inlineStr">
@@ -68090,22 +68118,22 @@
         </is>
       </c>
       <c r="BB254" s="5" t="n">
-        <v>46002.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BC254" s="5" t="n">
-        <v>46017.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BD254" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BE254" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF254" s="8" t="n">
-        <v>850400.58</v>
+      <c r="BF254" s="7" t="n">
+        <v>340161.0</v>
       </c>
       <c r="BG254" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BH254" s="11" t="inlineStr">
         <is>
@@ -68119,7 +68147,7 @@
       </c>
       <c r="BJ254" s="11" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
@@ -68222,7 +68250,7 @@
       </c>
       <c r="W255" s="11" t="inlineStr">
         <is>
-          <t>CPS-918-2025</t>
+          <t xml:space="preserve">	CPS-891-2025</t>
         </is>
       </c>
       <c r="X255" s="11" t="inlineStr">
@@ -68231,11 +68259,11 @@
         </is>
       </c>
       <c r="Y255" s="5" t="n">
-        <v>45925.0</v>
+        <v>45923.0</v>
       </c>
       <c r="Z255" s="11" t="inlineStr">
         <is>
-          <t>CO1.SLCNTR.15808066</t>
+          <t>CO1.SLCNTR.15791014</t>
         </is>
       </c>
       <c r="AA255" s="11" t="inlineStr">
@@ -68255,7 +68283,7 @@
       </c>
       <c r="AD255" s="11" t="inlineStr">
         <is>
-          <t>CPS-918-2025</t>
+          <t>CPS-891-2025</t>
         </is>
       </c>
       <c r="AE255" s="11" t="inlineStr">
@@ -68288,22 +68316,22 @@
       </c>
       <c r="AM255" s="11" t="inlineStr">
         <is>
-          <t>1102844070</t>
+          <t>1193228403</t>
         </is>
       </c>
       <c r="AN255" s="11" t="inlineStr">
         <is>
-          <t>FERNANDEZ ACOSTA GABRIELA</t>
+          <t>PATERNINA ALVAREZ MELISSA ALEJANDRA</t>
         </is>
       </c>
       <c r="AO255" s="11" t="inlineStr">
         <is>
-          <t>FERNANDEZ ACOSTA GABRIELA</t>
+          <t>PATERNINA ALVAREZ MELISSA ALEJANDRA</t>
         </is>
       </c>
       <c r="AP255" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+          <t/>
         </is>
       </c>
       <c r="AQ255" s="5" t="n">
@@ -68316,7 +68344,7 @@
         <v>46005.0</v>
       </c>
       <c r="AT255" s="5" t="n">
-        <v>45925.0</v>
+        <v>45923.0</v>
       </c>
       <c r="AU255" s="11" t="inlineStr">
         <is>
@@ -68362,7 +68390,7 @@
         <v>0.0</v>
       </c>
       <c r="BF255" s="8" t="n">
-        <v>850400.29</v>
+        <v>850400.58</v>
       </c>
       <c r="BG255" s="7" t="n">
         <v>1.309316E7</v>
@@ -68502,22 +68530,22 @@
       </c>
       <c r="AA256" s="11" t="inlineStr">
         <is>
-          <t>Contratación directa</t>
+          <t/>
         </is>
       </c>
       <c r="AB256" s="11" t="inlineStr">
         <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+          <t/>
         </is>
       </c>
       <c r="AC256" s="11" t="inlineStr">
         <is>
-          <t>Prestación de Servicios</t>
+          <t>SPGR Por definir</t>
         </is>
       </c>
       <c r="AD256" s="11" t="inlineStr">
         <is>
-          <t>CPS-1195-2025</t>
+          <t>CPS-1213-2025</t>
         </is>
       </c>
       <c r="AE256" s="11" t="inlineStr">
@@ -68525,14 +68553,14 @@
           <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
-      <c r="AF256" s="7" t="n">
-        <v>5237264.0</v>
-      </c>
-      <c r="AG256" s="7" t="n">
-        <v>5237264.0</v>
-      </c>
-      <c r="AH256" s="7" t="n">
-        <v>5237264.0</v>
+      <c r="AF256" s="8" t="n">
+        <v>2094905.06</v>
+      </c>
+      <c r="AG256" s="8" t="n">
+        <v>2094905.06</v>
+      </c>
+      <c r="AH256" s="8" t="n">
+        <v>2094905.06</v>
       </c>
       <c r="AI256" s="7" t="n">
         <v>0.0</v>
@@ -68545,22 +68573,22 @@
       </c>
       <c r="AL256" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">En ejecución                                                          </t>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
       <c r="AM256" s="11" t="inlineStr">
         <is>
-          <t>92033989</t>
+          <t>1066188077</t>
         </is>
       </c>
       <c r="AN256" s="11" t="inlineStr">
         <is>
-          <t>ROMERO PEREZ AMILCAR YESIT</t>
+          <t>DIAZ RIVAS JAIRO ENRIQUE</t>
         </is>
       </c>
       <c r="AO256" s="11" t="inlineStr">
         <is>
-          <t>ROMERO PEREZ AMILCAR YESIT</t>
+          <t>DIAZ RIVAS JAIRO ENRIQUE</t>
         </is>
       </c>
       <c r="AP256" s="11" t="inlineStr">
@@ -68568,17 +68596,23 @@
           <t/>
         </is>
       </c>
-      <c r="AQ256" s="5" t="n">
-        <v>45993.0</v>
-      </c>
-      <c r="AR256" s="5" t="n">
-        <v>46023.0</v>
-      </c>
-      <c r="AS256" s="5" t="n">
-        <v>46023.0</v>
+      <c r="AQ256" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR256" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS256" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AT256" s="5" t="n">
-        <v>45992.0</v>
+        <v>46009.0</v>
       </c>
       <c r="AU256" s="11" t="inlineStr">
         <is>
@@ -68587,23 +68621,27 @@
       </c>
       <c r="AV256" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="AW256" s="7" t="n">
-        <v>30.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AW256" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AX256" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
-        </is>
-      </c>
-      <c r="AY256" s="7" t="n">
-        <v>4.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AY256" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AZ256" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t/>
         </is>
       </c>
       <c r="BA256" s="11" t="inlineStr">
@@ -68612,22 +68650,22 @@
         </is>
       </c>
       <c r="BB256" s="5" t="n">
-        <v>46045.0</v>
+        <v>46093.0</v>
       </c>
       <c r="BC256" s="5" t="n">
-        <v>46045.0</v>
-      </c>
-      <c r="BD256" s="7" t="n">
-        <v>5237264.0</v>
+        <v>46093.0</v>
+      </c>
+      <c r="BD256" s="8" t="n">
+        <v>2094905.06</v>
       </c>
       <c r="BE256" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF256" s="7" t="n">
-        <v>340161.0</v>
-      </c>
-      <c r="BG256" s="7" t="n">
-        <v>5237264.0</v>
+        <v>136064.0</v>
+      </c>
+      <c r="BG256" s="8" t="n">
+        <v>2094905.06</v>
       </c>
       <c r="BH256" s="11" t="inlineStr">
         <is>
@@ -68641,7 +68679,7 @@
       </c>
       <c r="BJ256" s="11" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>03/01/2026</t>
         </is>
       </c>
     </row>
@@ -68779,7 +68817,7 @@
       </c>
       <c r="AD257" s="11" t="inlineStr">
         <is>
-          <t>CPS-1189-2025</t>
+          <t>CPS-1195-2025</t>
         </is>
       </c>
       <c r="AE257" s="11" t="inlineStr">
@@ -68788,13 +68826,13 @@
         </is>
       </c>
       <c r="AF257" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AG257" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AH257" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AI257" s="7" t="n">
         <v>0.0</v>
@@ -68812,32 +68850,32 @@
       </c>
       <c r="AM257" s="11" t="inlineStr">
         <is>
-          <t>1047478148</t>
+          <t>92033989</t>
         </is>
       </c>
       <c r="AN257" s="11" t="inlineStr">
         <is>
-          <t>Vanessa Stella Martínez Viloria</t>
+          <t>ROMERO PEREZ AMILCAR YESIT</t>
         </is>
       </c>
       <c r="AO257" s="11" t="inlineStr">
         <is>
-          <t>Vanessa Stella Martínez Viloria</t>
+          <t>ROMERO PEREZ AMILCAR YESIT</t>
         </is>
       </c>
       <c r="AP257" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+          <t/>
         </is>
       </c>
       <c r="AQ257" s="5" t="n">
-        <v>45992.0</v>
+        <v>45993.0</v>
       </c>
       <c r="AR257" s="5" t="n">
-        <v>46022.0</v>
+        <v>46023.0</v>
       </c>
       <c r="AS257" s="5" t="n">
-        <v>46022.0</v>
+        <v>46023.0</v>
       </c>
       <c r="AT257" s="5" t="n">
         <v>45992.0</v>
@@ -68880,16 +68918,16 @@
         <v>46045.0</v>
       </c>
       <c r="BD257" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="BE257" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF257" s="7" t="n">
-        <v>340160.0</v>
+        <v>340161.0</v>
       </c>
       <c r="BG257" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="BH257" s="11" t="inlineStr">
         <is>
@@ -69006,114 +69044,116 @@
       </c>
       <c r="W258" s="11" t="inlineStr">
         <is>
-          <t>CPS-885-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X258" s="11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y258" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z258" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA258" s="11" t="inlineStr">
+        <is>
+          <t>Contratación directa</t>
+        </is>
+      </c>
+      <c r="AB258" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+        </is>
+      </c>
+      <c r="AC258" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios</t>
+        </is>
+      </c>
+      <c r="AD258" s="11" t="inlineStr">
+        <is>
+          <t>CPS-1189-2025</t>
+        </is>
+      </c>
+      <c r="AE258" s="11" t="inlineStr">
+        <is>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF258" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AG258" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AH258" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AI258" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ258" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK258" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL258" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En ejecución                                                          </t>
+        </is>
+      </c>
+      <c r="AM258" s="11" t="inlineStr">
+        <is>
+          <t>1047478148</t>
+        </is>
+      </c>
+      <c r="AN258" s="11" t="inlineStr">
+        <is>
+          <t>Vanessa Stella Martínez Viloria</t>
+        </is>
+      </c>
+      <c r="AO258" s="11" t="inlineStr">
+        <is>
+          <t>Vanessa Stella Martínez Viloria</t>
+        </is>
+      </c>
+      <c r="AP258" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="AQ258" s="5" t="n">
+        <v>45992.0</v>
+      </c>
+      <c r="AR258" s="5" t="n">
+        <v>46022.0</v>
+      </c>
+      <c r="AS258" s="5" t="n">
+        <v>46022.0</v>
+      </c>
+      <c r="AT258" s="5" t="n">
+        <v>45992.0</v>
+      </c>
+      <c r="AU258" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV258" s="11" t="inlineStr">
+        <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="Y258" s="5" t="n">
-        <v>45924.0</v>
-      </c>
-      <c r="Z258" s="11" t="inlineStr">
-        <is>
-          <t>CO1.SLCNTR.15807689</t>
-        </is>
-      </c>
-      <c r="AA258" s="11" t="inlineStr">
-        <is>
-          <t>Contratación directa</t>
-        </is>
-      </c>
-      <c r="AB258" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
-        </is>
-      </c>
-      <c r="AC258" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de Servicios</t>
-        </is>
-      </c>
-      <c r="AD258" s="11" t="inlineStr">
-        <is>
-          <t>CPS-885-2025</t>
-        </is>
-      </c>
-      <c r="AE258" s="11" t="inlineStr">
-        <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF258" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AG258" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AH258" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AI258" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ258" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK258" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL258" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contratado sin ejecución                                              </t>
-        </is>
-      </c>
-      <c r="AM258" s="11" t="inlineStr">
-        <is>
-          <t>1102887805</t>
-        </is>
-      </c>
-      <c r="AN258" s="11" t="inlineStr">
-        <is>
-          <t>ALVAREZ URZOLA RODRIGO DE JESUS</t>
-        </is>
-      </c>
-      <c r="AO258" s="11" t="inlineStr">
-        <is>
-          <t>ALVAREZ URZOLA RODRIGO DE JESUS</t>
-        </is>
-      </c>
-      <c r="AP258" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
-        </is>
-      </c>
-      <c r="AQ258" s="5" t="n">
-        <v>45930.0</v>
-      </c>
-      <c r="AR258" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AS258" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AT258" s="5" t="n">
-        <v>45924.0</v>
-      </c>
-      <c r="AU258" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV258" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AW258" s="7" t="n">
-        <v>75.0</v>
+        <v>30.0</v>
       </c>
       <c r="AX258" s="11" t="inlineStr">
         <is>
@@ -69121,7 +69161,7 @@
         </is>
       </c>
       <c r="AY258" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ258" s="11" t="inlineStr">
         <is>
@@ -69134,22 +69174,22 @@
         </is>
       </c>
       <c r="BB258" s="5" t="n">
-        <v>45996.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BC258" s="5" t="n">
-        <v>46017.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BD258" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237261.0</v>
       </c>
       <c r="BE258" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF258" s="8" t="n">
-        <v>850400.58</v>
+      <c r="BF258" s="7" t="n">
+        <v>340160.0</v>
       </c>
       <c r="BG258" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237261.0</v>
       </c>
       <c r="BH258" s="11" t="inlineStr">
         <is>
@@ -69163,7 +69203,7 @@
       </c>
       <c r="BJ258" s="11" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
@@ -69266,7 +69306,7 @@
       </c>
       <c r="W259" s="11" t="inlineStr">
         <is>
-          <t>CPS-889-2025</t>
+          <t>CPS-885-2025</t>
         </is>
       </c>
       <c r="X259" s="11" t="inlineStr">
@@ -69275,11 +69315,11 @@
         </is>
       </c>
       <c r="Y259" s="5" t="n">
-        <v>45922.0</v>
+        <v>45924.0</v>
       </c>
       <c r="Z259" s="11" t="inlineStr">
         <is>
-          <t>CO1.SLCNTR.15794606</t>
+          <t>CO1.SLCNTR.15807689</t>
         </is>
       </c>
       <c r="AA259" s="11" t="inlineStr">
@@ -69299,7 +69339,7 @@
       </c>
       <c r="AD259" s="11" t="inlineStr">
         <is>
-          <t>CPS-889-2025</t>
+          <t>CPS-885-2025</t>
         </is>
       </c>
       <c r="AE259" s="11" t="inlineStr">
@@ -69332,22 +69372,22 @@
       </c>
       <c r="AM259" s="11" t="inlineStr">
         <is>
-          <t>1101451026</t>
+          <t>1102887805</t>
         </is>
       </c>
       <c r="AN259" s="11" t="inlineStr">
         <is>
-          <t>BLANCO VASQUEZ IRIS JOHANA</t>
+          <t>ALVAREZ URZOLA RODRIGO DE JESUS</t>
         </is>
       </c>
       <c r="AO259" s="11" t="inlineStr">
         <is>
-          <t>BLANCO VASQUEZ IRIS JOHANA</t>
+          <t>ALVAREZ URZOLA RODRIGO DE JESUS</t>
         </is>
       </c>
       <c r="AP259" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
         </is>
       </c>
       <c r="AQ259" s="5" t="n">
@@ -69360,7 +69400,7 @@
         <v>46005.0</v>
       </c>
       <c r="AT259" s="5" t="n">
-        <v>45922.0</v>
+        <v>45924.0</v>
       </c>
       <c r="AU259" s="11" t="inlineStr">
         <is>
@@ -69394,10 +69434,10 @@
         </is>
       </c>
       <c r="BB259" s="5" t="n">
-        <v>46014.0</v>
+        <v>45996.0</v>
       </c>
       <c r="BC259" s="5" t="n">
-        <v>46041.0</v>
+        <v>46017.0</v>
       </c>
       <c r="BD259" s="7" t="n">
         <v>1.309316E7</v>
@@ -69406,7 +69446,7 @@
         <v>0.0</v>
       </c>
       <c r="BF259" s="8" t="n">
-        <v>850401.29</v>
+        <v>850400.58</v>
       </c>
       <c r="BG259" s="7" t="n">
         <v>1.309316E7</v>
@@ -69526,7 +69566,7 @@
       </c>
       <c r="W260" s="11" t="inlineStr">
         <is>
-          <t>CPS-895-2025</t>
+          <t>CPS-889-2025</t>
         </is>
       </c>
       <c r="X260" s="11" t="inlineStr">
@@ -69535,11 +69575,11 @@
         </is>
       </c>
       <c r="Y260" s="5" t="n">
-        <v>45923.0</v>
+        <v>45922.0</v>
       </c>
       <c r="Z260" s="11" t="inlineStr">
         <is>
-          <t>CO1.SLCNTR.15793151</t>
+          <t>CO1.SLCNTR.15794606</t>
         </is>
       </c>
       <c r="AA260" s="11" t="inlineStr">
@@ -69559,7 +69599,7 @@
       </c>
       <c r="AD260" s="11" t="inlineStr">
         <is>
-          <t>CPS-895-2025</t>
+          <t>CPS-889-2025</t>
         </is>
       </c>
       <c r="AE260" s="11" t="inlineStr">
@@ -69592,17 +69632,17 @@
       </c>
       <c r="AM260" s="11" t="inlineStr">
         <is>
-          <t>1100307483</t>
+          <t>1101451026</t>
         </is>
       </c>
       <c r="AN260" s="11" t="inlineStr">
         <is>
-          <t>MENDEZ BARRETO JORGE IVAN</t>
+          <t>BLANCO VASQUEZ IRIS JOHANA</t>
         </is>
       </c>
       <c r="AO260" s="11" t="inlineStr">
         <is>
-          <t>MENDEZ BARRETO JORGE IVAN</t>
+          <t>BLANCO VASQUEZ IRIS JOHANA</t>
         </is>
       </c>
       <c r="AP260" s="11" t="inlineStr">
@@ -69620,7 +69660,7 @@
         <v>46005.0</v>
       </c>
       <c r="AT260" s="5" t="n">
-        <v>45923.0</v>
+        <v>45922.0</v>
       </c>
       <c r="AU260" s="11" t="inlineStr">
         <is>
@@ -69654,10 +69694,10 @@
         </is>
       </c>
       <c r="BB260" s="5" t="n">
-        <v>46002.0</v>
+        <v>46014.0</v>
       </c>
       <c r="BC260" s="5" t="n">
-        <v>46051.0</v>
+        <v>46041.0</v>
       </c>
       <c r="BD260" s="7" t="n">
         <v>1.309316E7</v>
@@ -69666,7 +69706,7 @@
         <v>0.0</v>
       </c>
       <c r="BF260" s="8" t="n">
-        <v>850400.58</v>
+        <v>850401.29</v>
       </c>
       <c r="BG260" s="7" t="n">
         <v>1.309316E7</v>
@@ -69786,22 +69826,20 @@
       </c>
       <c r="W261" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CPS-895-2025</t>
         </is>
       </c>
       <c r="X261" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y261" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="Y261" s="5" t="n">
+        <v>45923.0</v>
       </c>
       <c r="Z261" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>CO1.SLCNTR.15793151</t>
         </is>
       </c>
       <c r="AA261" s="11" t="inlineStr">
@@ -69821,22 +69859,22 @@
       </c>
       <c r="AD261" s="11" t="inlineStr">
         <is>
-          <t>CPS-1184-2025</t>
+          <t>CPS-895-2025</t>
         </is>
       </c>
       <c r="AE261" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF261" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AG261" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AH261" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AI261" s="7" t="n">
         <v>0.0</v>
@@ -69849,40 +69887,40 @@
       </c>
       <c r="AL261" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">En ejecución                                                          </t>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
       <c r="AM261" s="11" t="inlineStr">
         <is>
-          <t>17901255</t>
+          <t>1100307483</t>
         </is>
       </c>
       <c r="AN261" s="11" t="inlineStr">
         <is>
-          <t>Dustin Yamid Díaz Rangel cédula</t>
+          <t>MENDEZ BARRETO JORGE IVAN</t>
         </is>
       </c>
       <c r="AO261" s="11" t="inlineStr">
         <is>
-          <t>Dustin Yamid Díaz Rangel cédula</t>
+          <t>MENDEZ BARRETO JORGE IVAN</t>
         </is>
       </c>
       <c r="AP261" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+          <t/>
         </is>
       </c>
       <c r="AQ261" s="5" t="n">
-        <v>45992.0</v>
+        <v>45930.0</v>
       </c>
       <c r="AR261" s="5" t="n">
-        <v>46022.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AS261" s="5" t="n">
-        <v>46022.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AT261" s="5" t="n">
-        <v>45992.0</v>
+        <v>45923.0</v>
       </c>
       <c r="AU261" s="11" t="inlineStr">
         <is>
@@ -69895,7 +69933,7 @@
         </is>
       </c>
       <c r="AW261" s="7" t="n">
-        <v>30.0</v>
+        <v>75.0</v>
       </c>
       <c r="AX261" s="11" t="inlineStr">
         <is>
@@ -69903,7 +69941,7 @@
         </is>
       </c>
       <c r="AY261" s="7" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="AZ261" s="11" t="inlineStr">
         <is>
@@ -69916,22 +69954,22 @@
         </is>
       </c>
       <c r="BB261" s="5" t="n">
-        <v>46045.0</v>
+        <v>46002.0</v>
       </c>
       <c r="BC261" s="5" t="n">
-        <v>46045.0</v>
+        <v>46051.0</v>
       </c>
       <c r="BD261" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BE261" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF261" s="7" t="n">
-        <v>340161.0</v>
+      <c r="BF261" s="8" t="n">
+        <v>850400.58</v>
       </c>
       <c r="BG261" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BH261" s="11" t="inlineStr">
         <is>
@@ -69945,7 +69983,7 @@
       </c>
       <c r="BJ261" s="11" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
     </row>
@@ -70048,126 +70086,128 @@
       </c>
       <c r="W262" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">	CPS-891-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X262" s="11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y262" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z262" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA262" s="11" t="inlineStr">
+        <is>
+          <t>Contratación directa</t>
+        </is>
+      </c>
+      <c r="AB262" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+        </is>
+      </c>
+      <c r="AC262" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios</t>
+        </is>
+      </c>
+      <c r="AD262" s="11" t="inlineStr">
+        <is>
+          <t>CPS-1122-2025</t>
+        </is>
+      </c>
+      <c r="AE262" s="11" t="inlineStr">
+        <is>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR  EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF262" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AG262" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AH262" s="7" t="n">
+        <v>5237264.0</v>
+      </c>
+      <c r="AI262" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ262" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK262" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL262" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En ejecución                                                          </t>
+        </is>
+      </c>
+      <c r="AM262" s="11" t="inlineStr">
+        <is>
+          <t>64703642</t>
+        </is>
+      </c>
+      <c r="AN262" s="11" t="inlineStr">
+        <is>
+          <t>ORTEGA CASTIBLANCO KELLY JOHANA</t>
+        </is>
+      </c>
+      <c r="AO262" s="11" t="inlineStr">
+        <is>
+          <t>ORTEGA CASTIBLANCO KELLY JOHANA</t>
+        </is>
+      </c>
+      <c r="AP262" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ262" s="5" t="n">
+        <v>45989.0</v>
+      </c>
+      <c r="AR262" s="5" t="n">
+        <v>46018.0</v>
+      </c>
+      <c r="AS262" s="5" t="n">
+        <v>46018.0</v>
+      </c>
+      <c r="AT262" s="5" t="n">
+        <v>45989.0</v>
+      </c>
+      <c r="AU262" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV262" s="11" t="inlineStr">
+        <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="Y262" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="Z262" s="11" t="inlineStr">
-        <is>
-          <t>CO1.SLCNTR.15791014</t>
-        </is>
-      </c>
-      <c r="AA262" s="11" t="inlineStr">
-        <is>
-          <t>Contratación directa</t>
-        </is>
-      </c>
-      <c r="AB262" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
-        </is>
-      </c>
-      <c r="AC262" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de Servicios</t>
-        </is>
-      </c>
-      <c r="AD262" s="11" t="inlineStr">
-        <is>
-          <t>CPS-891-2025</t>
-        </is>
-      </c>
-      <c r="AE262" s="11" t="inlineStr">
-        <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF262" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AG262" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AH262" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AI262" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ262" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK262" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL262" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contratado sin ejecución                                              </t>
-        </is>
-      </c>
-      <c r="AM262" s="11" t="inlineStr">
-        <is>
-          <t>1193228403</t>
-        </is>
-      </c>
-      <c r="AN262" s="11" t="inlineStr">
-        <is>
-          <t>PATERNINA ALVAREZ MELISSA ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="AO262" s="11" t="inlineStr">
-        <is>
-          <t>PATERNINA ALVAREZ MELISSA ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="AP262" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ262" s="5" t="n">
-        <v>45930.0</v>
-      </c>
-      <c r="AR262" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AS262" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AT262" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="AU262" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV262" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AW262" s="7" t="n">
-        <v>75.0</v>
+        <v>1.0</v>
       </c>
       <c r="AX262" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="AY262" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ262" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia(s)              </t>
+          <t xml:space="preserve">Mes(es)             </t>
         </is>
       </c>
       <c r="BA262" s="11" t="inlineStr">
@@ -70176,22 +70216,22 @@
         </is>
       </c>
       <c r="BB262" s="5" t="n">
-        <v>46000.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BC262" s="5" t="n">
-        <v>46017.0</v>
+        <v>46049.0</v>
       </c>
       <c r="BD262" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BE262" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF262" s="8" t="n">
-        <v>850400.58</v>
+      <c r="BF262" s="7" t="n">
+        <v>340161.0</v>
       </c>
       <c r="BG262" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BH262" s="11" t="inlineStr">
         <is>
@@ -70205,7 +70245,7 @@
       </c>
       <c r="BJ262" s="11" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
@@ -70308,22 +70348,20 @@
       </c>
       <c r="W263" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CPS-924-2025</t>
         </is>
       </c>
       <c r="X263" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y263" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="Y263" s="5" t="n">
+        <v>45923.0</v>
       </c>
       <c r="Z263" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>CO1.SLCNTR.15801022</t>
         </is>
       </c>
       <c r="AA263" s="11" t="inlineStr">
@@ -70343,22 +70381,22 @@
       </c>
       <c r="AD263" s="11" t="inlineStr">
         <is>
-          <t>CPS-1186-2025</t>
+          <t>CPS-924-2025</t>
         </is>
       </c>
       <c r="AE263" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF263" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AG263" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AH263" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="AI263" s="7" t="n">
         <v>0.0</v>
@@ -70371,40 +70409,40 @@
       </c>
       <c r="AL263" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">En ejecución                                                          </t>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
       <c r="AM263" s="11" t="inlineStr">
         <is>
-          <t>1102821657</t>
+          <t>1102820744</t>
         </is>
       </c>
       <c r="AN263" s="11" t="inlineStr">
         <is>
-          <t>Miryan del Carmen Sampayo Vergara</t>
+          <t>BENITEZ FRANCO FABIO ANDRES</t>
         </is>
       </c>
       <c r="AO263" s="11" t="inlineStr">
         <is>
-          <t>Miryan del Carmen Sampayo Vergara</t>
+          <t>BENITEZ FRANCO FABIO ANDRES</t>
         </is>
       </c>
       <c r="AP263" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+          <t/>
         </is>
       </c>
       <c r="AQ263" s="5" t="n">
-        <v>45992.0</v>
+        <v>45930.0</v>
       </c>
       <c r="AR263" s="5" t="n">
-        <v>46022.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AS263" s="5" t="n">
-        <v>46022.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AT263" s="5" t="n">
-        <v>45992.0</v>
+        <v>45923.0</v>
       </c>
       <c r="AU263" s="11" t="inlineStr">
         <is>
@@ -70413,11 +70451,11 @@
       </c>
       <c r="AV263" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t/>
         </is>
       </c>
       <c r="AW263" s="7" t="n">
-        <v>30.0</v>
+        <v>75.0</v>
       </c>
       <c r="AX263" s="11" t="inlineStr">
         <is>
@@ -70425,7 +70463,7 @@
         </is>
       </c>
       <c r="AY263" s="7" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="AZ263" s="11" t="inlineStr">
         <is>
@@ -70438,22 +70476,22 @@
         </is>
       </c>
       <c r="BB263" s="5" t="n">
-        <v>46049.0</v>
+        <v>46002.0</v>
       </c>
       <c r="BC263" s="5" t="n">
-        <v>46049.0</v>
+        <v>46017.0</v>
       </c>
       <c r="BD263" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BE263" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF263" s="7" t="n">
-        <v>340161.0</v>
+      <c r="BF263" s="8" t="n">
+        <v>850400.58</v>
       </c>
       <c r="BG263" s="7" t="n">
-        <v>5237264.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BH263" s="11" t="inlineStr">
         <is>
@@ -70467,7 +70505,7 @@
       </c>
       <c r="BJ263" s="11" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
     </row>
@@ -70605,7 +70643,7 @@
       </c>
       <c r="AD264" s="11" t="inlineStr">
         <is>
-          <t>CPS-1181-2025</t>
+          <t>CPS-1183-2025</t>
         </is>
       </c>
       <c r="AE264" s="11" t="inlineStr">
@@ -70614,13 +70652,13 @@
         </is>
       </c>
       <c r="AF264" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AG264" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AH264" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="AI264" s="7" t="n">
         <v>0.0</v>
@@ -70638,17 +70676,17 @@
       </c>
       <c r="AM264" s="11" t="inlineStr">
         <is>
-          <t>22884384</t>
+          <t>1102828243</t>
         </is>
       </c>
       <c r="AN264" s="11" t="inlineStr">
         <is>
-          <t>ELVIA ISABEL VERGARA GIL.</t>
+          <t xml:space="preserve">Yuranis Astrid Morón Fuentes </t>
         </is>
       </c>
       <c r="AO264" s="11" t="inlineStr">
         <is>
-          <t>ELVIA ISABEL VERGARA GIL.</t>
+          <t xml:space="preserve">Yuranis Astrid Morón Fuentes </t>
         </is>
       </c>
       <c r="AP264" s="11" t="inlineStr">
@@ -70706,16 +70744,16 @@
         <v>46045.0</v>
       </c>
       <c r="BD264" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="BE264" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF264" s="7" t="n">
-        <v>340160.0</v>
+        <v>340161.0</v>
       </c>
       <c r="BG264" s="7" t="n">
-        <v>5237261.0</v>
+        <v>5237264.0</v>
       </c>
       <c r="BH264" s="11" t="inlineStr">
         <is>
@@ -70867,12 +70905,12 @@
       </c>
       <c r="AD265" s="11" t="inlineStr">
         <is>
-          <t>CPS-1143-2025</t>
+          <t>CPS-1186-2025</t>
         </is>
       </c>
       <c r="AE265" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR  EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF265" s="7" t="n">
@@ -70900,35 +70938,35 @@
       </c>
       <c r="AM265" s="11" t="inlineStr">
         <is>
-          <t>1005659848</t>
+          <t>1102821657</t>
         </is>
       </c>
       <c r="AN265" s="11" t="inlineStr">
         <is>
-          <t>ORDOÑEZ VERGARA MAYLEN JOSE</t>
+          <t>Miryan del Carmen Sampayo Vergara</t>
         </is>
       </c>
       <c r="AO265" s="11" t="inlineStr">
         <is>
-          <t>ORDOÑEZ VERGARA MAYLEN JOSE</t>
+          <t>Miryan del Carmen Sampayo Vergara</t>
         </is>
       </c>
       <c r="AP265" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
         </is>
       </c>
       <c r="AQ265" s="5" t="n">
-        <v>45989.0</v>
+        <v>45992.0</v>
       </c>
       <c r="AR265" s="5" t="n">
-        <v>46018.0</v>
+        <v>46022.0</v>
       </c>
       <c r="AS265" s="5" t="n">
-        <v>46018.0</v>
+        <v>46022.0</v>
       </c>
       <c r="AT265" s="5" t="n">
-        <v>45989.0</v>
+        <v>45992.0</v>
       </c>
       <c r="AU265" s="11" t="inlineStr">
         <is>
@@ -70941,11 +70979,11 @@
         </is>
       </c>
       <c r="AW265" s="7" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="AX265" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="AY265" s="7" t="n">
@@ -70953,7 +70991,7 @@
       </c>
       <c r="AZ265" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="BA265" s="11" t="inlineStr">
@@ -71094,114 +71132,116 @@
       </c>
       <c r="W266" s="11" t="inlineStr">
         <is>
-          <t>CPS-892-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X266" s="11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y266" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z266" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA266" s="11" t="inlineStr">
+        <is>
+          <t>Contratación directa</t>
+        </is>
+      </c>
+      <c r="AB266" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
+        </is>
+      </c>
+      <c r="AC266" s="11" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios</t>
+        </is>
+      </c>
+      <c r="AD266" s="11" t="inlineStr">
+        <is>
+          <t>CPS-1181-2025</t>
+        </is>
+      </c>
+      <c r="AE266" s="11" t="inlineStr">
+        <is>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF266" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AG266" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AH266" s="7" t="n">
+        <v>5237261.0</v>
+      </c>
+      <c r="AI266" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ266" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK266" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL266" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En ejecución                                                          </t>
+        </is>
+      </c>
+      <c r="AM266" s="11" t="inlineStr">
+        <is>
+          <t>22884384</t>
+        </is>
+      </c>
+      <c r="AN266" s="11" t="inlineStr">
+        <is>
+          <t>ELVIA ISABEL VERGARA GIL.</t>
+        </is>
+      </c>
+      <c r="AO266" s="11" t="inlineStr">
+        <is>
+          <t>ELVIA ISABEL VERGARA GIL.</t>
+        </is>
+      </c>
+      <c r="AP266" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="AQ266" s="5" t="n">
+        <v>45992.0</v>
+      </c>
+      <c r="AR266" s="5" t="n">
+        <v>46022.0</v>
+      </c>
+      <c r="AS266" s="5" t="n">
+        <v>46022.0</v>
+      </c>
+      <c r="AT266" s="5" t="n">
+        <v>45992.0</v>
+      </c>
+      <c r="AU266" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV266" s="11" t="inlineStr">
+        <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="Y266" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="Z266" s="11" t="inlineStr">
-        <is>
-          <t>CO1.SLCNTR.15801345</t>
-        </is>
-      </c>
-      <c r="AA266" s="11" t="inlineStr">
-        <is>
-          <t>Contratación directa</t>
-        </is>
-      </c>
-      <c r="AB266" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
-        </is>
-      </c>
-      <c r="AC266" s="11" t="inlineStr">
-        <is>
-          <t>Prestación de Servicios</t>
-        </is>
-      </c>
-      <c r="AD266" s="11" t="inlineStr">
-        <is>
-          <t>CPS-892-2025</t>
-        </is>
-      </c>
-      <c r="AE266" s="11" t="inlineStr">
-        <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF266" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AG266" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AH266" s="7" t="n">
-        <v>1.309316E7</v>
-      </c>
-      <c r="AI266" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ266" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK266" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL266" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contratado sin ejecución                                              </t>
-        </is>
-      </c>
-      <c r="AM266" s="11" t="inlineStr">
-        <is>
-          <t>1005566510</t>
-        </is>
-      </c>
-      <c r="AN266" s="11" t="inlineStr">
-        <is>
-          <t>HERRERA CERVANTES VALERIA</t>
-        </is>
-      </c>
-      <c r="AO266" s="11" t="inlineStr">
-        <is>
-          <t>HERRERA CERVANTES VALERIA</t>
-        </is>
-      </c>
-      <c r="AP266" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ266" s="5" t="n">
-        <v>45930.0</v>
-      </c>
-      <c r="AR266" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AS266" s="5" t="n">
-        <v>46005.0</v>
-      </c>
-      <c r="AT266" s="5" t="n">
-        <v>45923.0</v>
-      </c>
-      <c r="AU266" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV266" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AW266" s="7" t="n">
-        <v>75.0</v>
+        <v>30.0</v>
       </c>
       <c r="AX266" s="11" t="inlineStr">
         <is>
@@ -71209,7 +71249,7 @@
         </is>
       </c>
       <c r="AY266" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ266" s="11" t="inlineStr">
         <is>
@@ -71222,22 +71262,22 @@
         </is>
       </c>
       <c r="BB266" s="5" t="n">
-        <v>46001.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BC266" s="5" t="n">
-        <v>46017.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BD266" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237261.0</v>
       </c>
       <c r="BE266" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF266" s="8" t="n">
-        <v>850401.29</v>
+      <c r="BF266" s="7" t="n">
+        <v>340160.0</v>
       </c>
       <c r="BG266" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237261.0</v>
       </c>
       <c r="BH266" s="11" t="inlineStr">
         <is>
@@ -71251,7 +71291,7 @@
       </c>
       <c r="BJ266" s="11" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
@@ -71354,20 +71394,22 @@
       </c>
       <c r="W267" s="11" t="inlineStr">
         <is>
-          <t>CPS-864-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X267" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="Y267" s="5" t="n">
-        <v>45924.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="Y267" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="Z267" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CO1_PCCNTR_8361792_</t>
+          <t/>
         </is>
       </c>
       <c r="AA267" s="11" t="inlineStr">
@@ -71387,22 +71429,22 @@
       </c>
       <c r="AD267" s="11" t="inlineStr">
         <is>
-          <t>CPS-864-2025</t>
+          <t>CPS-1184-2025</t>
         </is>
       </c>
       <c r="AE267" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF267" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="AG267" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="AH267" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="AI267" s="7" t="n">
         <v>0.0</v>
@@ -71420,46 +71462,48 @@
       </c>
       <c r="AM267" s="11" t="inlineStr">
         <is>
-          <t>1102873021</t>
+          <t>17901255</t>
         </is>
       </c>
       <c r="AN267" s="11" t="inlineStr">
         <is>
-          <t>CABALLERO CAPELLA EMIRO ANDRES</t>
+          <t>Dustin Yamid Díaz Rangel cédula</t>
         </is>
       </c>
       <c r="AO267" s="11" t="inlineStr">
         <is>
-          <t>CABALLERO CAPELLA EMIRO ANDRES</t>
+          <t>Dustin Yamid Díaz Rangel cédula</t>
         </is>
       </c>
       <c r="AP267" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Persona Natural                                                                                                                                       </t>
         </is>
       </c>
       <c r="AQ267" s="5" t="n">
-        <v>45930.0</v>
+        <v>45992.0</v>
       </c>
       <c r="AR267" s="5" t="n">
-        <v>46005.0</v>
+        <v>46022.0</v>
       </c>
       <c r="AS267" s="5" t="n">
-        <v>46005.0</v>
+        <v>46022.0</v>
       </c>
       <c r="AT267" s="5" t="n">
-        <v>45924.0</v>
-      </c>
-      <c r="AU267" s="5" t="n">
-        <v>45924.0</v>
+        <v>45992.0</v>
+      </c>
+      <c r="AU267" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AV267" s="11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t/>
         </is>
       </c>
       <c r="AW267" s="7" t="n">
-        <v>75.0</v>
+        <v>30.0</v>
       </c>
       <c r="AX267" s="11" t="inlineStr">
         <is>
@@ -71467,7 +71511,7 @@
         </is>
       </c>
       <c r="AY267" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="AZ267" s="11" t="inlineStr">
         <is>
@@ -71480,22 +71524,22 @@
         </is>
       </c>
       <c r="BB267" s="5" t="n">
-        <v>45996.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BC267" s="5" t="n">
-        <v>46017.0</v>
+        <v>46045.0</v>
       </c>
       <c r="BD267" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BE267" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF267" s="8" t="n">
-        <v>850400.58</v>
+      <c r="BF267" s="7" t="n">
+        <v>340161.0</v>
       </c>
       <c r="BG267" s="7" t="n">
-        <v>1.309316E7</v>
+        <v>5237264.0</v>
       </c>
       <c r="BH267" s="11" t="inlineStr">
         <is>
@@ -71509,7 +71553,7 @@
       </c>
       <c r="BJ267" s="11" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
@@ -71612,57 +71656,55 @@
       </c>
       <c r="W268" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CPS-892-2025</t>
         </is>
       </c>
       <c r="X268" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="Y268" s="5" t="n">
+        <v>45923.0</v>
       </c>
       <c r="Z268" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>CO1.SLCNTR.15801345</t>
         </is>
       </c>
       <c r="AA268" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>Contratación directa</t>
         </is>
       </c>
       <c r="AB268" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
         </is>
       </c>
       <c r="AC268" s="11" t="inlineStr">
         <is>
-          <t>SPGR Por definir</t>
+          <t>Prestación de Servicios</t>
         </is>
       </c>
       <c r="AD268" s="11" t="inlineStr">
         <is>
-          <t>CPS-1213-2025</t>
+          <t>CPS-892-2025</t>
         </is>
       </c>
       <c r="AE268" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF268" s="8" t="n">
-        <v>2094905.06</v>
-      </c>
-      <c r="AG268" s="8" t="n">
-        <v>2094905.06</v>
-      </c>
-      <c r="AH268" s="8" t="n">
-        <v>2094905.06</v>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF268" s="7" t="n">
+        <v>1.309316E7</v>
+      </c>
+      <c r="AG268" s="7" t="n">
+        <v>1.309316E7</v>
+      </c>
+      <c r="AH268" s="7" t="n">
+        <v>1.309316E7</v>
       </c>
       <c r="AI268" s="7" t="n">
         <v>0.0</v>
@@ -71680,17 +71722,17 @@
       </c>
       <c r="AM268" s="11" t="inlineStr">
         <is>
-          <t>1066188077</t>
+          <t>1005566510</t>
         </is>
       </c>
       <c r="AN268" s="11" t="inlineStr">
         <is>
-          <t>DIAZ RIVAS JAIRO ENRIQUE</t>
+          <t>HERRERA CERVANTES VALERIA</t>
         </is>
       </c>
       <c r="AO268" s="11" t="inlineStr">
         <is>
-          <t>DIAZ RIVAS JAIRO ENRIQUE</t>
+          <t>HERRERA CERVANTES VALERIA</t>
         </is>
       </c>
       <c r="AP268" s="11" t="inlineStr">
@@ -71698,23 +71740,17 @@
           <t/>
         </is>
       </c>
-      <c r="AQ268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AR268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AS268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="AQ268" s="5" t="n">
+        <v>45930.0</v>
+      </c>
+      <c r="AR268" s="5" t="n">
+        <v>46005.0</v>
+      </c>
+      <c r="AS268" s="5" t="n">
+        <v>46005.0</v>
       </c>
       <c r="AT268" s="5" t="n">
-        <v>46009.0</v>
+        <v>45923.0</v>
       </c>
       <c r="AU268" s="11" t="inlineStr">
         <is>
@@ -71726,24 +71762,20 @@
           <t/>
         </is>
       </c>
-      <c r="AW268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="AW268" s="7" t="n">
+        <v>75.0</v>
       </c>
       <c r="AX268" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY268" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t xml:space="preserve">Dia(s)              </t>
+        </is>
+      </c>
+      <c r="AY268" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="AZ268" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="BA268" s="11" t="inlineStr">
@@ -71752,22 +71784,22 @@
         </is>
       </c>
       <c r="BB268" s="5" t="n">
-        <v>46093.0</v>
+        <v>46001.0</v>
       </c>
       <c r="BC268" s="5" t="n">
-        <v>46093.0</v>
-      </c>
-      <c r="BD268" s="8" t="n">
-        <v>2094905.06</v>
+        <v>46017.0</v>
+      </c>
+      <c r="BD268" s="7" t="n">
+        <v>1.309316E7</v>
       </c>
       <c r="BE268" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF268" s="7" t="n">
-        <v>136064.0</v>
-      </c>
-      <c r="BG268" s="8" t="n">
-        <v>2094905.06</v>
+      <c r="BF268" s="8" t="n">
+        <v>850401.29</v>
+      </c>
+      <c r="BG268" s="7" t="n">
+        <v>1.309316E7</v>
       </c>
       <c r="BH268" s="11" t="inlineStr">
         <is>
@@ -71781,7 +71813,7 @@
       </c>
       <c r="BJ268" s="11" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
     </row>
@@ -71818,7 +71850,7 @@
       </c>
       <c r="G269" s="11" t="inlineStr">
         <is>
-          <t>GALERAS</t>
+          <t>SUCRE</t>
         </is>
       </c>
       <c r="H269" s="11" t="inlineStr">
@@ -71849,17 +71881,17 @@
       </c>
       <c r="N269" s="11" t="inlineStr">
         <is>
-          <t>2025000020037</t>
+          <t>2025000020019</t>
         </is>
       </c>
       <c r="O269" s="11" t="inlineStr">
         <is>
-          <t>Pavimentación de la vía que conduce de la cabecera del municipio de Galeras hasta el corregimiento de Santiago Apóstol jurisdicción del municipio de San Benito Abad Departamento de  Sucre</t>
+          <t>Implementación del programa de alimentación escolar -PAE- para el segundo semestre del 2025 en el Departamento de   Sucre</t>
         </is>
       </c>
       <c r="P269" s="11" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>EDUCACIÓN</t>
         </is>
       </c>
       <c r="Q269" s="11" t="inlineStr">
@@ -71867,8 +71899,8 @@
           <t/>
         </is>
       </c>
-      <c r="R269" s="8" t="n">
-        <v>7.971560177168E10</v>
+      <c r="R269" s="7" t="n">
+        <v>1.5884181916E10</v>
       </c>
       <c r="S269" s="7" t="n">
         <v>0.0</v>
@@ -71879,60 +71911,60 @@
       <c r="U269" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="V269" s="8" t="n">
-        <v>7.971560177168E10</v>
+      <c r="V269" s="7" t="n">
+        <v>1.5884181916E10</v>
       </c>
       <c r="W269" s="11" t="inlineStr">
         <is>
-          <t>CONV 023-2025</t>
+          <t>CPS-864-2025</t>
         </is>
       </c>
       <c r="X269" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="Y269" s="5" t="n">
-        <v>45849.0</v>
+        <v>45924.0</v>
       </c>
       <c r="Z269" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t xml:space="preserve"> CO1_PCCNTR_8361792_</t>
         </is>
       </c>
       <c r="AA269" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>Contratación directa</t>
         </is>
       </c>
       <c r="AB269" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>Prestación de servicios profesionales y de apoyo a la gestión, o para la ejecución de trabajos artísticos. (Decreto 734 de 2012/Decreto 1510 de 2013)</t>
         </is>
       </c>
       <c r="AC269" s="11" t="inlineStr">
         <is>
-          <t>SPGR Por definir</t>
+          <t>Prestación de Servicios</t>
         </is>
       </c>
       <c r="AD269" s="11" t="inlineStr">
         <is>
-          <t>CONV-023-2025</t>
+          <t>CPS-864-2025</t>
         </is>
       </c>
       <c r="AE269" s="11" t="inlineStr">
         <is>
-          <t>PRESTACION DE SERVICIOS DE GERENCIA INTEGRAL Y ADMINISTRACION DE RECURSOS PARA EL COMPONENTE DE LA INTERVENTORIA TECNICA, ADMINISTRATIVA, FINANCIERA, AMBIENTAL, SOCIAL, Y SEGURIDAD EN EL TRABAJO AL PROYECTO DE PAVIMENTACION DE LA VIA QUE CONDUCE DE LA CABECERA MUNICIPAL DE GALERAS, SUCRE HASTA EL CORREGIMIENTO DE SANTIAGO APOSTOL MUNICIPIO DE GASLERAS EN EL DEPARTAMENTO DE SUCRE.</t>
-        </is>
-      </c>
-      <c r="AF269" s="8" t="n">
-        <v>3.78228270448E9</v>
-      </c>
-      <c r="AG269" s="8" t="n">
-        <v>3.78228270448E9</v>
-      </c>
-      <c r="AH269" s="8" t="n">
-        <v>3.78228270448E9</v>
+          <t>PRESTACION DE SERVICIOS PROFESIONALES PARA APOYAR EL DESARROLLO DE ACCIONES EN EL MARCO DE LA IMPLEMENTACION DEL PROGRAMA DE ALIMENTACION ESCOLAR PAE PARA EL SEGUNDO SEMESTRE DEL 2025 EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF269" s="7" t="n">
+        <v>1.309316E7</v>
+      </c>
+      <c r="AG269" s="7" t="n">
+        <v>1.309316E7</v>
+      </c>
+      <c r="AH269" s="7" t="n">
+        <v>1.309316E7</v>
       </c>
       <c r="AI269" s="7" t="n">
         <v>0.0</v>
@@ -71950,66 +71982,58 @@
       </c>
       <c r="AM269" s="11" t="inlineStr">
         <is>
-          <t>901848109</t>
+          <t>1102873021</t>
         </is>
       </c>
       <c r="AN269" s="11" t="inlineStr">
         <is>
-          <t>EMPRESA PROMOTORA DE BOLIVAR - "RUTA B"</t>
+          <t>CABALLERO CAPELLA EMIRO ANDRES</t>
         </is>
       </c>
       <c r="AO269" s="11" t="inlineStr">
         <is>
-          <t>ADRIANA MARGARITA TRUCCO DE LA  HOZ</t>
+          <t>CABALLERO CAPELLA EMIRO ANDRES</t>
         </is>
       </c>
       <c r="AP269" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empresa Industrial y Comercial del Estado                                                                                                             </t>
+          <t/>
         </is>
       </c>
       <c r="AQ269" s="5" t="n">
-        <v>46038.0</v>
-      </c>
-      <c r="AR269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>45930.0</v>
+      </c>
+      <c r="AR269" s="5" t="n">
+        <v>46005.0</v>
       </c>
       <c r="AS269" s="5" t="n">
-        <v>46038.0</v>
+        <v>46005.0</v>
       </c>
       <c r="AT269" s="5" t="n">
-        <v>46009.0</v>
-      </c>
-      <c r="AU269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>45924.0</v>
+      </c>
+      <c r="AU269" s="5" t="n">
+        <v>45924.0</v>
       </c>
       <c r="AV269" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AW269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="AW269" s="7" t="n">
+        <v>75.0</v>
       </c>
       <c r="AX269" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t xml:space="preserve">Dia(s)              </t>
+        </is>
+      </c>
+      <c r="AY269" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="AZ269" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Dia(s)              </t>
         </is>
       </c>
       <c r="BA269" s="11" t="inlineStr">
@@ -72017,27 +72041,23 @@
           <t>N</t>
         </is>
       </c>
-      <c r="BB269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BC269" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="BB269" s="5" t="n">
+        <v>45996.0</v>
+      </c>
+      <c r="BC269" s="5" t="n">
+        <v>46017.0</v>
       </c>
       <c r="BD269" s="7" t="n">
-        <v>0.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BE269" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BF269" s="7" t="n">
-        <v>0.0</v>
+      <c r="BF269" s="8" t="n">
+        <v>850400.58</v>
       </c>
       <c r="BG269" s="7" t="n">
-        <v>0.0</v>
+        <v>1.309316E7</v>
       </c>
       <c r="BH269" s="11" t="inlineStr">
         <is>
@@ -72051,7 +72071,7 @@
       </c>
       <c r="BJ269" s="11" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
     </row>
@@ -72154,22 +72174,20 @@
       </c>
       <c r="W270" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CONV 023-2025</t>
         </is>
       </c>
       <c r="X270" s="11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y270" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y270" s="5" t="n">
+        <v>45849.0</v>
       </c>
       <c r="Z270" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AA270" s="11" t="inlineStr">
@@ -72189,22 +72207,22 @@
       </c>
       <c r="AD270" s="11" t="inlineStr">
         <is>
-          <t>LP-008-2025</t>
+          <t>CONV-023-2025</t>
         </is>
       </c>
       <c r="AE270" s="11" t="inlineStr">
         <is>
-          <t>PAVIMENTACION DE LA VIA QUE CONDUCE DE LA CABECERA MUNICIPAL DEL MUNICIPIO DE GALERAS SUCRE HASTA SANTIAGO APOSTOL DEPARTAMENTO DE SUCRE</t>
-        </is>
-      </c>
-      <c r="AF270" s="7" t="n">
-        <v>7.2251935328E10</v>
-      </c>
-      <c r="AG270" s="7" t="n">
-        <v>7.2251935328E10</v>
-      </c>
-      <c r="AH270" s="7" t="n">
-        <v>7.2251935328E10</v>
+          <t>PRESTACION DE SERVICIOS DE GERENCIA INTEGRAL Y ADMINISTRACION DE RECURSOS PARA EL COMPONENTE DE LA INTERVENTORIA TECNICA, ADMINISTRATIVA, FINANCIERA, AMBIENTAL, SOCIAL, Y SEGURIDAD EN EL TRABAJO AL PROYECTO DE PAVIMENTACION DE LA VIA QUE CONDUCE DE LA CABECERA MUNICIPAL DE GALERAS, SUCRE HASTA EL CORREGIMIENTO DE SANTIAGO APOSTOL MUNICIPIO DE GASLERAS EN EL DEPARTAMENTO DE SUCRE.</t>
+        </is>
+      </c>
+      <c r="AF270" s="8" t="n">
+        <v>3.78228270448E9</v>
+      </c>
+      <c r="AG270" s="8" t="n">
+        <v>3.78228270448E9</v>
+      </c>
+      <c r="AH270" s="8" t="n">
+        <v>3.78228270448E9</v>
       </c>
       <c r="AI270" s="7" t="n">
         <v>0.0</v>
@@ -72222,26 +72240,26 @@
       </c>
       <c r="AM270" s="11" t="inlineStr">
         <is>
-          <t>902024964</t>
+          <t>901848109</t>
         </is>
       </c>
       <c r="AN270" s="11" t="inlineStr">
         <is>
-          <t>CONSORCIO CABECERA VIAL SUCRE</t>
+          <t>EMPRESA PROMOTORA DE BOLIVAR - "RUTA B"</t>
         </is>
       </c>
       <c r="AO270" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t>ADRIANA MARGARITA TRUCCO DE LA  HOZ</t>
         </is>
       </c>
       <c r="AP270" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Empresa Industrial y Comercial del Estado                                                                                                             </t>
         </is>
       </c>
       <c r="AQ270" s="5" t="n">
-        <v>46064.0</v>
+        <v>46038.0</v>
       </c>
       <c r="AR270" s="11" t="inlineStr">
         <is>
@@ -72249,10 +72267,10 @@
         </is>
       </c>
       <c r="AS270" s="5" t="n">
-        <v>46064.0</v>
+        <v>46038.0</v>
       </c>
       <c r="AT270" s="5" t="n">
-        <v>46058.0</v>
+        <v>46009.0</v>
       </c>
       <c r="AU270" s="11" t="inlineStr">
         <is>
@@ -72289,23 +72307,27 @@
           <t>N</t>
         </is>
       </c>
-      <c r="BB270" s="5" t="n">
-        <v>46086.0</v>
-      </c>
-      <c r="BC270" s="5" t="n">
-        <v>46149.0</v>
-      </c>
-      <c r="BD270" s="8" t="n">
-        <v>2.79476992104E10</v>
+      <c r="BB270" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC270" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD270" s="7" t="n">
+        <v>0.0</v>
       </c>
       <c r="BE270" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF270" s="7" t="n">
-        <v>4.150114096E9</v>
-      </c>
-      <c r="BG270" s="8" t="n">
-        <v>2.79476992104E10</v>
+        <v>0.0</v>
+      </c>
+      <c r="BG270" s="7" t="n">
+        <v>0.0</v>
       </c>
       <c r="BH270" s="11" t="inlineStr">
         <is>
@@ -72319,7 +72341,7 @@
       </c>
       <c r="BJ270" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
     </row>
@@ -72331,17 +72353,17 @@
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>DEPARTAMENTALES</t>
+          <t>REGIONALES</t>
         </is>
       </c>
       <c r="C271" s="11" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE SUCRE</t>
+          <t>Región Caribe</t>
         </is>
       </c>
       <c r="D271" s="11" t="inlineStr">
         <is>
-          <t>SUCRE</t>
+          <t>Región Caribe</t>
         </is>
       </c>
       <c r="E271" s="11" t="inlineStr">
@@ -72356,7 +72378,7 @@
       </c>
       <c r="G271" s="11" t="inlineStr">
         <is>
-          <t>SUCRE</t>
+          <t>GALERAS</t>
         </is>
       </c>
       <c r="H271" s="11" t="inlineStr">
@@ -72387,17 +72409,17 @@
       </c>
       <c r="N271" s="11" t="inlineStr">
         <is>
-          <t>2025002700015</t>
+          <t>2025000020037</t>
         </is>
       </c>
       <c r="O271" s="11" t="inlineStr">
         <is>
-          <t>Elaboración de estudios técnicos y jurídicos para el saneamiento de bienes baldíos urbanos con fines de titulación en municipios del departamento de  Sucre</t>
+          <t>Pavimentación de la vía que conduce de la cabecera del municipio de Galeras hasta el corregimiento de Santiago Apóstol jurisdicción del municipio de San Benito Abad Departamento de  Sucre</t>
         </is>
       </c>
       <c r="P271" s="11" t="inlineStr">
         <is>
-          <t>VIVIENDA, CIUDAD Y TERRITORIO</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="Q271" s="11" t="inlineStr">
@@ -72405,8 +72427,8 @@
           <t/>
         </is>
       </c>
-      <c r="R271" s="7" t="n">
-        <v>1.000000435E9</v>
+      <c r="R271" s="8" t="n">
+        <v>7.971560177168E10</v>
       </c>
       <c r="S271" s="7" t="n">
         <v>0.0</v>
@@ -72417,60 +72439,62 @@
       <c r="U271" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="V271" s="7" t="n">
-        <v>1.000000435E9</v>
+      <c r="V271" s="8" t="n">
+        <v>7.971560177168E10</v>
       </c>
       <c r="W271" s="11" t="inlineStr">
         <is>
-          <t>CM-008-2025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X271" s="11" t="inlineStr">
         <is>
-          <t>5608</t>
-        </is>
-      </c>
-      <c r="Y271" s="5" t="n">
-        <v>45981.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="Y271" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="Z271" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t/>
         </is>
       </c>
       <c r="AA271" s="11" t="inlineStr">
         <is>
-          <t>Concurso de méritos</t>
+          <t/>
         </is>
       </c>
       <c r="AB271" s="11" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t/>
         </is>
       </c>
       <c r="AC271" s="11" t="inlineStr">
         <is>
-          <t>Consultoría</t>
+          <t>SPGR Por definir</t>
         </is>
       </c>
       <c r="AD271" s="11" t="inlineStr">
         <is>
-          <t>CM-008-2025</t>
+          <t>LP-008-2025</t>
         </is>
       </c>
       <c r="AE271" s="11" t="inlineStr">
         <is>
-          <t>CONSULTORIA PARA LA ELOBORACION DE ESTUDIOS TECNICOS Y JURIDICOS PARA EL SANEAMIENTO DE BIENES BALDIOS URBANOS CON FINES DE TITULACION EN MUNICIPIOS DEL DEPARTAMENTO DE SUCRE</t>
+          <t>PAVIMENTACION DE LA VIA QUE CONDUCE DE LA CABECERA MUNICIPAL DEL MUNICIPIO DE GALERAS SUCRE HASTA SANTIAGO APOSTOL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF271" s="7" t="n">
-        <v>1.000000435E9</v>
+        <v>7.2251935328E10</v>
       </c>
       <c r="AG271" s="7" t="n">
-        <v>1.000000435E9</v>
+        <v>7.2251935328E10</v>
       </c>
       <c r="AH271" s="7" t="n">
-        <v>1.000000435E9</v>
+        <v>7.2251935328E10</v>
       </c>
       <c r="AI271" s="7" t="n">
         <v>0.0</v>
@@ -72488,58 +72512,66 @@
       </c>
       <c r="AM271" s="11" t="inlineStr">
         <is>
-          <t>901983356</t>
+          <t>902024964</t>
         </is>
       </c>
       <c r="AN271" s="11" t="inlineStr">
         <is>
-          <t>SILVA Y SILVA CONSULTORIA S.A.S.</t>
+          <t>CONSORCIO CABECERA VIAL SUCRE</t>
         </is>
       </c>
       <c r="AO271" s="11" t="inlineStr">
         <is>
-          <t>Luis Ricardo Padilla Brunal</t>
+          <t/>
         </is>
       </c>
       <c r="AP271" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sociedad Por Acciones Simplificadas                                                                                                                   </t>
+          <t/>
         </is>
       </c>
       <c r="AQ271" s="5" t="n">
-        <v>46009.0</v>
-      </c>
-      <c r="AR271" s="5" t="n">
-        <v>46190.0</v>
+        <v>46064.0</v>
+      </c>
+      <c r="AR271" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AS271" s="5" t="n">
-        <v>46190.0</v>
+        <v>46064.0</v>
       </c>
       <c r="AT271" s="5" t="n">
-        <v>46008.0</v>
-      </c>
-      <c r="AU271" s="5" t="n">
-        <v>45996.0</v>
+        <v>46058.0</v>
+      </c>
+      <c r="AU271" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AV271" s="11" t="inlineStr">
         <is>
-          <t>5911</t>
-        </is>
-      </c>
-      <c r="AW271" s="7" t="n">
-        <v>6.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AW271" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AX271" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
-        </is>
-      </c>
-      <c r="AY271" s="7" t="n">
-        <v>6.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AY271" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AZ271" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes(es)             </t>
+          <t/>
         </is>
       </c>
       <c r="BA271" s="11" t="inlineStr">
@@ -72548,22 +72580,22 @@
         </is>
       </c>
       <c r="BB271" s="5" t="n">
-        <v>46020.0</v>
+        <v>46086.0</v>
       </c>
       <c r="BC271" s="5" t="n">
-        <v>46020.0</v>
+        <v>46149.0</v>
       </c>
       <c r="BD271" s="8" t="n">
-        <v>3.000001305E8</v>
+        <v>2.79476992104E10</v>
       </c>
       <c r="BE271" s="7" t="n">
         <v>0.0</v>
       </c>
       <c r="BF271" s="7" t="n">
-        <v>0.0</v>
+        <v>4.150114096E9</v>
       </c>
       <c r="BG271" s="8" t="n">
-        <v>3.000001305E8</v>
+        <v>2.79476992104E10</v>
       </c>
       <c r="BH271" s="11" t="inlineStr">
         <is>
@@ -72577,7 +72609,7 @@
       </c>
       <c r="BJ271" s="11" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
     </row>
@@ -72645,17 +72677,17 @@
       </c>
       <c r="N272" s="11" t="inlineStr">
         <is>
-          <t>2025002700023</t>
+          <t>2025002700015</t>
         </is>
       </c>
       <c r="O272" s="11" t="inlineStr">
         <is>
-          <t>Estudio y diseño para la masificación de gas combustible domiciliario por redes para la zona rural de los municipios de San Onofre San antonio de Palmito Tolú Caimito y El Roble del Departamento de Sucre.  Sucre</t>
+          <t>Elaboración de estudios técnicos y jurídicos para el saneamiento de bienes baldíos urbanos con fines de titulación en municipios del departamento de  Sucre</t>
         </is>
       </c>
       <c r="P272" s="11" t="inlineStr">
         <is>
-          <t>MINAS Y ENERGÍA</t>
+          <t>VIVIENDA, CIUDAD Y TERRITORIO</t>
         </is>
       </c>
       <c r="Q272" s="11" t="inlineStr">
@@ -72664,7 +72696,7 @@
         </is>
       </c>
       <c r="R272" s="7" t="n">
-        <v>1.26567201E9</v>
+        <v>1.000000435E9</v>
       </c>
       <c r="S272" s="7" t="n">
         <v>0.0</v>
@@ -72676,24 +72708,24 @@
         <v>0.0</v>
       </c>
       <c r="V272" s="7" t="n">
-        <v>1.26567201E9</v>
+        <v>1.000000435E9</v>
       </c>
       <c r="W272" s="11" t="inlineStr">
         <is>
-          <t>CM-001-2026</t>
+          <t>CM-008-2025</t>
         </is>
       </c>
       <c r="X272" s="11" t="inlineStr">
         <is>
-          <t>0767</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="Y272" s="5" t="n">
-        <v>46076.0</v>
+        <v>45981.0</v>
       </c>
       <c r="Z272" s="11" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AA272" s="11" t="inlineStr">
@@ -72713,22 +72745,22 @@
       </c>
       <c r="AD272" s="11" t="inlineStr">
         <is>
-          <t>CM-001-2026</t>
+          <t>CM-008-2025</t>
         </is>
       </c>
       <c r="AE272" s="11" t="inlineStr">
         <is>
-          <t>ESTUDIO DE FACTIBILIDAD Y DISEÑO PARA LA MASIFICACIÓN DE GAS COMBUSTIBLE DOMICILIARIO POR REDES PARA LA ZONA RURAL DE LOS MUNICIPIOS DE SAN ONOFRE, SAN ANTONIO DE PALMITO, TOLÚ, CAIMITO Y EL ROBLE, DEL DEPARTAMENTO DE SUCRE</t>
+          <t>CONSULTORIA PARA LA ELOBORACION DE ESTUDIOS TECNICOS Y JURIDICOS PARA EL SANEAMIENTO DE BIENES BALDIOS URBANOS CON FINES DE TITULACION EN MUNICIPIOS DEL DEPARTAMENTO DE SUCRE</t>
         </is>
       </c>
       <c r="AF272" s="7" t="n">
-        <v>1.265672005E9</v>
+        <v>1.000000435E9</v>
       </c>
       <c r="AG272" s="7" t="n">
-        <v>1.265672005E9</v>
+        <v>1.000000435E9</v>
       </c>
       <c r="AH272" s="7" t="n">
-        <v>1.265672005E9</v>
+        <v>1.000000435E9</v>
       </c>
       <c r="AI272" s="7" t="n">
         <v>0.0</v>
@@ -72746,46 +72778,46 @@
       </c>
       <c r="AM272" s="11" t="inlineStr">
         <is>
-          <t>72184399</t>
+          <t>901983356</t>
         </is>
       </c>
       <c r="AN272" s="11" t="inlineStr">
         <is>
-          <t>CONTRERAS MADRID ISMAEL GREGORIO</t>
+          <t>SILVA Y SILVA CONSULTORIA S.A.S.</t>
         </is>
       </c>
       <c r="AO272" s="11" t="inlineStr">
         <is>
-          <t>CONTRERAS MADRID ISMAEL GREGORIO</t>
+          <t>Luis Ricardo Padilla Brunal</t>
         </is>
       </c>
       <c r="AP272" s="11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Sociedad Por Acciones Simplificadas                                                                                                                   </t>
         </is>
       </c>
       <c r="AQ272" s="5" t="n">
-        <v>46139.0</v>
+        <v>46009.0</v>
       </c>
       <c r="AR272" s="5" t="n">
-        <v>46199.0</v>
+        <v>46190.0</v>
       </c>
       <c r="AS272" s="5" t="n">
-        <v>46199.0</v>
+        <v>46190.0</v>
       </c>
       <c r="AT272" s="5" t="n">
-        <v>46094.0</v>
+        <v>46008.0</v>
       </c>
       <c r="AU272" s="5" t="n">
-        <v>46094.0</v>
+        <v>45996.0</v>
       </c>
       <c r="AV272" s="11" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="AW272" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="AX272" s="11" t="inlineStr">
         <is>
@@ -72805,18 +72837,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="BB272" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BC272" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BD272" s="7" t="n">
-        <v>0.0</v>
+      <c r="BB272" s="5" t="n">
+        <v>46020.0</v>
+      </c>
+      <c r="BC272" s="5" t="n">
+        <v>46020.0</v>
+      </c>
+      <c r="BD272" s="8" t="n">
+        <v>3.000001305E8</v>
       </c>
       <c r="BE272" s="7" t="n">
         <v>0.0</v>
@@ -72824,8 +72852,8 @@
       <c r="BF272" s="7" t="n">
         <v>0.0</v>
       </c>
-      <c r="BG272" s="7" t="n">
-        <v>0.0</v>
+      <c r="BG272" s="8" t="n">
+        <v>3.000001305E8</v>
       </c>
       <c r="BH272" s="11" t="inlineStr">
         <is>
@@ -72839,7 +72867,7 @@
       </c>
       <c r="BJ272" s="11" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
     </row>
@@ -72907,213 +72935,751 @@
       </c>
       <c r="N273" s="11" t="inlineStr">
         <is>
+          <t>2025002700019</t>
+        </is>
+      </c>
+      <c r="O273" s="11" t="inlineStr">
+        <is>
+          <t>Mejoramiento de la Institución Educativa El Mamón sede principal en el municipio de Corozal departamento de   Sucre</t>
+        </is>
+      </c>
+      <c r="P273" s="11" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="Q273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R273" s="8" t="n">
+        <v>9.1027185128E8</v>
+      </c>
+      <c r="S273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V273" s="8" t="n">
+        <v>9.1027185128E8</v>
+      </c>
+      <c r="W273" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC273" s="11" t="inlineStr">
+        <is>
+          <t>SPGR Por definir</t>
+        </is>
+      </c>
+      <c r="AD273" s="11" t="inlineStr">
+        <is>
+          <t>SA-003-2026</t>
+        </is>
+      </c>
+      <c r="AE273" s="11" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO DE LA INSTITUCION EDUCATIVA EL MAMON, SEDE PRINCIPAL, EN EL MUNICIPIO DE COROZAL EN EL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF273" s="8" t="n">
+        <v>8.0953204497E8</v>
+      </c>
+      <c r="AG273" s="8" t="n">
+        <v>8.0953204497E8</v>
+      </c>
+      <c r="AH273" s="8" t="n">
+        <v>8.0953204497E8</v>
+      </c>
+      <c r="AI273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL273" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratado sin ejecución                                              </t>
+        </is>
+      </c>
+      <c r="AM273" s="11" t="inlineStr">
+        <is>
+          <t>902055164</t>
+        </is>
+      </c>
+      <c r="AN273" s="11" t="inlineStr">
+        <is>
+          <t>CONSORCIO IE EL MAMON</t>
+        </is>
+      </c>
+      <c r="AO273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT273" s="5" t="n">
+        <v>46163.0</v>
+      </c>
+      <c r="AU273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA273" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BB273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BG273" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BI273" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ273" s="11" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>CARIBE</t>
+        </is>
+      </c>
+      <c r="B274" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTALES</t>
+        </is>
+      </c>
+      <c r="C274" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="D274" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="E274" s="11" t="inlineStr">
+        <is>
+          <t>CARIBE</t>
+        </is>
+      </c>
+      <c r="F274" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="G274" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="H274" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="I274" s="7" t="n">
+        <v>70000.0</v>
+      </c>
+      <c r="J274" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="K274" s="7" t="n">
+        <v>70000.0</v>
+      </c>
+      <c r="L274" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="M274" s="11" t="inlineStr">
+        <is>
+          <t>8922800211</t>
+        </is>
+      </c>
+      <c r="N274" s="11" t="inlineStr">
+        <is>
+          <t>2025002700023</t>
+        </is>
+      </c>
+      <c r="O274" s="11" t="inlineStr">
+        <is>
+          <t>Estudio y diseño para la masificación de gas combustible domiciliario por redes para la zona rural de los municipios de San Onofre San antonio de Palmito Tolú Caimito y El Roble del Departamento de Sucre.  Sucre</t>
+        </is>
+      </c>
+      <c r="P274" s="11" t="inlineStr">
+        <is>
+          <t>MINAS Y ENERGÍA</t>
+        </is>
+      </c>
+      <c r="Q274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R274" s="7" t="n">
+        <v>1.26567201E9</v>
+      </c>
+      <c r="S274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V274" s="7" t="n">
+        <v>1.26567201E9</v>
+      </c>
+      <c r="W274" s="11" t="inlineStr">
+        <is>
+          <t>CM-001-2026</t>
+        </is>
+      </c>
+      <c r="X274" s="11" t="inlineStr">
+        <is>
+          <t>0767</t>
+        </is>
+      </c>
+      <c r="Y274" s="5" t="n">
+        <v>46076.0</v>
+      </c>
+      <c r="Z274" s="11" t="inlineStr">
+        <is>
+          <t>S/N</t>
+        </is>
+      </c>
+      <c r="AA274" s="11" t="inlineStr">
+        <is>
+          <t>Concurso de méritos</t>
+        </is>
+      </c>
+      <c r="AB274" s="11" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC274" s="11" t="inlineStr">
+        <is>
+          <t>Consultoría</t>
+        </is>
+      </c>
+      <c r="AD274" s="11" t="inlineStr">
+        <is>
+          <t>CM-001-2026</t>
+        </is>
+      </c>
+      <c r="AE274" s="11" t="inlineStr">
+        <is>
+          <t>ESTUDIO DE FACTIBILIDAD Y DISEÑO PARA LA MASIFICACIÓN DE GAS COMBUSTIBLE DOMICILIARIO POR REDES PARA LA ZONA RURAL DE LOS MUNICIPIOS DE SAN ONOFRE, SAN ANTONIO DE PALMITO, TOLÚ, CAIMITO Y EL ROBLE, DEL DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="AF274" s="7" t="n">
+        <v>1.265672005E9</v>
+      </c>
+      <c r="AG274" s="7" t="n">
+        <v>1.265672005E9</v>
+      </c>
+      <c r="AH274" s="7" t="n">
+        <v>1.265672005E9</v>
+      </c>
+      <c r="AI274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL274" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En ejecución                                                          </t>
+        </is>
+      </c>
+      <c r="AM274" s="11" t="inlineStr">
+        <is>
+          <t>72184399</t>
+        </is>
+      </c>
+      <c r="AN274" s="11" t="inlineStr">
+        <is>
+          <t>CONTRERAS MADRID ISMAEL GREGORIO</t>
+        </is>
+      </c>
+      <c r="AO274" s="11" t="inlineStr">
+        <is>
+          <t>CONTRERAS MADRID ISMAEL GREGORIO</t>
+        </is>
+      </c>
+      <c r="AP274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ274" s="5" t="n">
+        <v>46139.0</v>
+      </c>
+      <c r="AR274" s="5" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="AS274" s="5" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="AT274" s="5" t="n">
+        <v>46094.0</v>
+      </c>
+      <c r="AU274" s="5" t="n">
+        <v>46094.0</v>
+      </c>
+      <c r="AV274" s="11" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="AW274" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AX274" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mes(es)             </t>
+        </is>
+      </c>
+      <c r="AY274" s="7" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="AZ274" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mes(es)             </t>
+        </is>
+      </c>
+      <c r="BA274" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BB274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BG274" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BI274" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ274" s="11" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>CARIBE</t>
+        </is>
+      </c>
+      <c r="B275" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTALES</t>
+        </is>
+      </c>
+      <c r="C275" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="D275" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="E275" s="11" t="inlineStr">
+        <is>
+          <t>CARIBE</t>
+        </is>
+      </c>
+      <c r="F275" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="G275" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="H275" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="I275" s="7" t="n">
+        <v>70000.0</v>
+      </c>
+      <c r="J275" s="11" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="K275" s="7" t="n">
+        <v>70000.0</v>
+      </c>
+      <c r="L275" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE SUCRE</t>
+        </is>
+      </c>
+      <c r="M275" s="11" t="inlineStr">
+        <is>
+          <t>8922800211</t>
+        </is>
+      </c>
+      <c r="N275" s="11" t="inlineStr">
+        <is>
           <t>2025002700025</t>
         </is>
       </c>
-      <c r="O273" s="11" t="inlineStr">
+      <c r="O275" s="11" t="inlineStr">
         <is>
           <t>Cofinanciación DE SUBSIDIO AL CARGO POR CONEXIÓN CERTIFICACION PREVIA E INSTALACIÓN INTERNA DEL SERVICIO DE GAS NATURAL PARA USUARIOS ESTRATO 1 Y 2 DE LOS CORREGIMIENTOS DE BARAYA (GALERAS) Y CIENAGUITA (TOLUVIEJO) Y DE LOS SECTORESBARRIOS CASTAÑEDA (SINCELEJO) Y ARROYO SECO (TOLUVIEJO) DEL DEPARTAMENTO DE  Sucre</t>
         </is>
       </c>
-      <c r="P273" s="11" t="inlineStr">
+      <c r="P275" s="11" t="inlineStr">
         <is>
           <t>MINAS Y ENERGÍA</t>
         </is>
       </c>
-      <c r="Q273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R273" s="7" t="n">
+      <c r="Q275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R275" s="7" t="n">
         <v>1.63128139E9</v>
       </c>
-      <c r="S273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T273" s="7" t="n">
+      <c r="S275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T275" s="7" t="n">
         <v>4.1120776E7</v>
       </c>
-      <c r="U273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="V273" s="7" t="n">
+      <c r="U275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V275" s="7" t="n">
         <v>1.672402166E9</v>
       </c>
-      <c r="W273" s="11" t="inlineStr">
+      <c r="W275" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC273" s="11" t="inlineStr">
+      <c r="X275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC275" s="11" t="inlineStr">
         <is>
           <t>SPGR Por definir</t>
         </is>
       </c>
-      <c r="AD273" s="11" t="inlineStr">
+      <c r="AD275" s="11" t="inlineStr">
         <is>
           <t>CONV-001-2026</t>
         </is>
       </c>
-      <c r="AE273" s="11" t="inlineStr">
+      <c r="AE275" s="11" t="inlineStr">
         <is>
           <t>ANUAR ESFUERZOS PARA LA COFINANCIACIÓN DE SUBSIDIO AL CARGO POR CONEXIÓN, CERTIFICACIÓN PREVIA E INSTALACIÓN INTERNA DEL SERVICIO DE GAS NATURAL PARA USUARIOS ESTRATOS 1 Y 2 DE LOS CORREGIMIENTOS BARAYA (GALERAS), CIENAGUITA Y ARROYO SECO (TOLUVIEJO), Y DEL SECTOR CASTAÑEDA (SINCELEJO), DEPARTAMENTO DE SUCRE- BPIN 2025002700025</t>
         </is>
       </c>
-      <c r="AF273" s="7" t="n">
+      <c r="AF275" s="7" t="n">
         <v>1.63128139E9</v>
       </c>
-      <c r="AG273" s="7" t="n">
+      <c r="AG275" s="7" t="n">
         <v>1.63128139E9</v>
       </c>
-      <c r="AH273" s="7" t="n">
+      <c r="AH275" s="7" t="n">
         <v>1.63128139E9</v>
       </c>
-      <c r="AI273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL273" s="11" t="inlineStr">
+      <c r="AI275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL275" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Contratado sin ejecución                                              </t>
         </is>
       </c>
-      <c r="AM273" s="11" t="inlineStr">
+      <c r="AM275" s="11" t="inlineStr">
         <is>
           <t>890400869</t>
         </is>
       </c>
-      <c r="AN273" s="11" t="inlineStr">
+      <c r="AN275" s="11" t="inlineStr">
         <is>
           <t>SURTIDORA DE GAS DEL CARIBE S.A SURTIGAS</t>
         </is>
       </c>
-      <c r="AO273" s="11" t="inlineStr">
+      <c r="AO275" s="11" t="inlineStr">
         <is>
           <t>SANTIAGO MEJIA MEDINA</t>
         </is>
       </c>
-      <c r="AP273" s="11" t="inlineStr">
+      <c r="AP275" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Empresa de servicios públicos                                                                                                                         </t>
         </is>
       </c>
-      <c r="AQ273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AR273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AS273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AT273" s="5" t="n">
+      <c r="AQ275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT275" s="5" t="n">
         <v>46057.0</v>
       </c>
-      <c r="AU273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AW273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AX273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AZ273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BA273" s="11" t="inlineStr">
+      <c r="AU275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA275" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BB273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BC273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BD273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BE273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BF273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BG273" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BH273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BI273" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BJ273" s="11" t="inlineStr">
+      <c r="BB275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BG275" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BI275" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ275" s="11" t="inlineStr">
         <is>
           <t>05/02/2026</t>
         </is>
@@ -73287,13 +73853,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD831B29-703E-4131-98BD-62FA7778544F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11F3AEEF-4F0C-4338-A585-D1DDEFFE41C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7DF20A4-B446-4786-906C-46A00DC13B4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D25221B-8EF1-451C-B679-0D369FA9C92E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4399960-6EB1-4043-AD7F-3D0589C94763}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5844301B-BF5F-4EFF-8B21-B7F208FC99B4}"/>
 </file>
--- a/data/CG-cttos.xlsx
+++ b/data/CG-cttos.xlsx
@@ -35868,7 +35868,7 @@
         <v>46194.0</v>
       </c>
       <c r="AT131" s="5" t="n">
-        <v>45709.0</v>
+        <v>45650.0</v>
       </c>
       <c r="AU131" s="5" t="n">
         <v>45589.0</v>
@@ -73835,13 +73835,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51E46EF1-D336-4C55-A18D-2BBF6E5622B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4013A0-BBD3-4C9E-AF9E-DF28A59015B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{346E8287-3049-484C-899F-E529A1D709C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22476FDD-9234-4F87-8B93-09E3DFE77868}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF2178B6-309E-4760-B24B-2298D64C3949}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15B55CD7-16E7-4C9D-BA0A-71C4BF9DCD27}"/>
 </file>